--- a/step_esg_pipeline/report.xlsx
+++ b/step_esg_pipeline/report.xlsx
@@ -590,7 +590,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Audit Timestamp: 2026-09-21 06:38 UTC | Scoped Links: 48 | Section: ESG Legislative Landscape</t>
+          <t>Audit Timestamp: 2026-09-21 07:28 UTC | Scoped Links: 48 | Section: ESG Legislative Landscape</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>https://www.greenfinanceplatform.org/policies-and-regulations/chinas-administrative-measures-legal-disclosure-enterprise-environmental?__cf_chl_rt_tk=nVXxt_nhEhdGbVyI_Z0wd6anvjr0.FJdLCDJf31KFPc-1789972400-1.0.1.1-NzuPhnYqj8us0obna6LvG1QTaKyo44evmyU3fNDOGU8</t>
+          <t>https://www.greenfinanceplatform.org/policies-and-regulations/chinas-administrative-measures-legal-disclosure-enterprise-environmental?__cf_chl_rt_tk=7288OQ.YtRNiXMXLWQZx1UTkIPnlBDkCHlljymeEwZE-1789975288-1.0.1.1-g.Ca2akZTj5DrhP1DOGBoaG4ofWiSID_KcHT2g1iGwI</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>BOT_PROTECTION</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -1250,7 +1250,7 @@
         <is>
           <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.greenfinanceplatform.org) (Domain www.greenfinanceplatform.org registered under China)
 4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
 5. (Identity): Regulatory identity: www.greenfinanceplatform.org (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UNKNOWN)
@@ -1645,153 +1645,154 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex')
 5. (Identity): Regulatory identity: EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: SUPERSEDED (Document explicitly superseded/repealed by the following: ‘(5) “net turnover” means the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed by the following: ‘(5) “net turnover” means the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>ESG Legislative Landscape</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>European Union</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript is disabled</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Regulation</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Directive</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Due Diligence &amp; Supply Chain</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Listed Companies / Issuers</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Large Enterprises / PIEs</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:32023DC0012https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>ACCESS_BLOCKED</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>Official Journal of the European Union</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="8" t="inlineStr">
         <is>
           <t>TIER_1_OFFICIAL_REGULATOR</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
         <is>
           <t>https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="Q11" s="8" t="inlineStr">
         <is>
           <t>Commission Delegated Regulation (EU) 2023/2772 (ESRS Set 1)</t>
         </is>
       </c>
-      <c r="R11" s="5" t="inlineStr">
+      <c r="R11" s="8" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="S11" s="5" t="inlineStr">
-        <is>
-          <t>CANDIDATE_UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="T11" s="5" t="inlineStr">
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>REPLACEMENT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>REPLACEMENT</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
+      <c r="U11" s="7" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="W11" s="4" t="inlineStr">
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL_REVIEW</t>
-        </is>
-      </c>
-      <c r="AB11" s="5" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
+      <c r="X11" s="7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="Y11" s="7" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="Z11" s="7" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="AA11" s="7" t="inlineStr">
+        <is>
+          <t>REPLACE</t>
+        </is>
+      </c>
+      <c r="AB11" s="8" t="inlineStr">
+        <is>
+          <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Identity): Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)
-6. (Discovery): Replacement candidate identified: https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng (Candidate title: 'Commission Delegated Regulation (EU) 2023/2772 (ESRS Set 1)', Verified: False)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Delegated regulation - EU - 2023/2772 - EN - EUR-Lex')
+5. (Identity): Regulatory identity: Delegated regulation - EU - 2023/2772 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Large Enterprises / PIEs, Authority: Official Journal of the European Union)
+6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)
+7. (Discovery): Replacement candidate identified: https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng (Candidate title: 'Commission Delegated Regulation (EU) 2023/2772 (ESRS Set 1)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -2040,9 +2041,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex')
 5. (Identity): Regulatory identity: EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
@@ -2166,9 +2167,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
 5. (Identity): Regulatory identity: Search results - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -2292,9 +2293,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex')
 5. (Identity): Regulatory identity: Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex (Consultation / Draft) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -2321,17 +2322,17 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Regulation</t>
+          <t>Directive</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Due Diligence &amp; Supply Chain</t>
+          <t>Climate &amp; Emissions Disclosure</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -2351,7 +2352,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr"/>
@@ -2367,7 +2368,7 @@
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="P16" s="5" t="inlineStr"/>
@@ -2381,7 +2382,7 @@
       <c r="T16" s="5" t="inlineStr"/>
       <c r="U16" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
@@ -2396,7 +2397,7 @@
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="Y16" s="4" t="inlineStr">
@@ -2406,7 +2407,7 @@
       </c>
       <c r="Z16" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="AA16" s="4" t="inlineStr">
@@ -2418,10 +2419,11 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Identity): Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex')
+5. (Identity): Regulatory identity: EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -2543,9 +2545,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex')
 5. (Identity): Regulatory identity: EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
@@ -2669,9 +2671,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
 5. (Identity): Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: SUPERSEDED (Document explicitly superseded/repealed) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed)</t>
         </is>
@@ -2795,9 +2797,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
 5. (Identity): Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -2824,12 +2826,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Regulation</t>
+          <t>Delegated Regulation</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2854,7 +2856,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr"/>
@@ -2878,30 +2880,30 @@
       <c r="R20" s="5" t="inlineStr"/>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>NONE_FOUND</t>
+          <t>NO_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr"/>
       <c r="U20" s="4" t="inlineStr">
         <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="X20" s="4" t="inlineStr">
+        <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
           <t>20%</t>
@@ -2909,7 +2911,7 @@
       </c>
       <c r="Z20" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="AA20" s="4" t="inlineStr">
@@ -2921,10 +2923,11 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Identity): Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
+5. (Identity): Regulatory identity: Search results - EUR-Lex (Delegated Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3077,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Error page</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Guideline / Standard</t>
+          <t>Act / Legislation</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3171,10 +3174,10 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)
+2. (Technical): HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Corporate Affairs (MCA)) (Domain www.mca.gov.in registered under India)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Error page')
-5. (Identity): Regulatory identity: Error page (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Ministry of Corporate Affairs (MCA))
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'HOME')
+5. (Identity): Regulatory identity: HOME (Act / Legislation) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Ministry of Corporate Affairs (MCA))
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Corporate Affairs (MCA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
@@ -3548,9 +3551,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Kuwait' (Exact match with target jurisdiction: 'Kuwait')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)
+2. (Technical): HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Boursa Kuwait) (Domain www.boursakuwait.com.kw registered under Kuwait)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'ESG Reporting Guide')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'ESG Reporting Guide')
 5. (Identity): Regulatory identity: ESG Reporting Guide (Guideline / Standard) (Topic: Corporate Governance &amp; CSR, Population: Listed Companies / Issuers, Authority: Boursa Kuwait)
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Boursa Kuwait (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -3933,145 +3936,127 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>ESG Legislative Landscape</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Guideline / Standard</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Sustainable Finance &amp; Green Bonds</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Listed Companies / Issuers</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mas.gov.sg/-/media/MAS/News-and-Publications/Consultation-Papers/CP13-Guidelines-on-Environmental-Risk-Management/Guidelines_on_Environmental_Risk_Management.pdf</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mas.gov.sg/-/media/MAS/News-and-Publications/Consultation-Papers/CP13-Guidelines-on-Environmental-Risk-Management/Guidelines_on_Environmental_Risk_Management.pdf</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Monetary Authority of Singapore (MAS)</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>TIER_1_OFFICIAL_REGULATOR</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Guideline / Standard</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Sustainable Finance &amp; Green Bonds</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Listed Companies / Issuers</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>https://www.mas.gov.sg/-/media/MAS/News-and-Publications/Consultation-Papers/CP13-Guidelines-on-Environmental-Risk-Management/Guidelines_on_Environmental_Risk_Management.pdf</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>https://www.mas.gov.sg/Custom/errorpages/PageNotFound.aspx</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>HTTP_404</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr"/>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t>Monetary Authority of Singapore (MAS)</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>TIER_1_OFFICIAL_REGULATOR</t>
-        </is>
-      </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="P29" s="9" t="inlineStr">
-        <is>
-          <t>https://www.mas.gov.sg/regulation/guidelines/guidelines-on-environmental-risk-management</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
-        <is>
-          <t>Monetary Authority of Singapore (MAS) Guidelines on Environmental Risk Management</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t>REPLACEMENT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>REPLACEMENT</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>NO_REPLACEMENT_REQUIRED</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr"/>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="V29" s="7" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="W29" s="7" t="inlineStr">
+      <c r="W29" s="4" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="X29" s="7" t="inlineStr">
+      <c r="X29" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="Y29" s="7" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="Z29" s="7" t="inlineStr">
+      <c r="Y29" s="4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="AA29" s="7" t="inlineStr">
-        <is>
-          <t>REPLACE</t>
-        </is>
-      </c>
-      <c r="AB29" s="8" t="inlineStr">
-        <is>
-          <t>Why was this marked REPLACE?
+      <c r="AA29" s="4" t="inlineStr">
+        <is>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="AB29" s="5" t="inlineStr">
+        <is>
+          <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')
-2. (Technical): Redirect detected (healthy_redirect) to: https://www.mas.gov.sg/Custom/errorpages/PageNotFound.aspx (Redirect chain length: 1)
-3. (Technical): HTTP 404 (HTTP_404) (Content-Type: text/html; charset=utf-8, Latency: 0ms)
-4. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
-5. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)
-7. (Discovery): Replacement candidate identified: https://www.mas.gov.sg/regulation/guidelines/guidelines-on-environmental-risk-management (Candidate title: 'Monetary Authority of Singapore (MAS) Guidelines on Environmental Risk Management', Verified: True)</t>
+2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
+4. (Identity): Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
+5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4081,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Guidelines on Environmental Risk Management for Asset Managers</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -4106,12 +4091,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Climate &amp; Emissions Disclosure</t>
+          <t>Sustainable Finance &amp; Green Bonds</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Financial Institutions / Asset Managers</t>
+          <t>Listed Companies / Issuers</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -4193,9 +4178,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')
-2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)
+2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
-4. (Identity): Regulatory identity: Guidelines on Environmental Risk Management for Asset Managers (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Financial Institutions / Asset Managers, Authority: Monetary Authority of Singapore (MAS))
+4. (Identity): Regulatory identity: Maintenance (Regulation) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
 5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
@@ -4221,7 +4206,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -4318,9 +4303,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')
-2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)
+2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
-4. (Identity): Regulatory identity: Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
+4. (Identity): Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
 5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
@@ -4897,7 +4882,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
@@ -4921,30 +4906,30 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="5" t="inlineStr">
         <is>
-          <t>NONE_FOUND</t>
+          <t>NO_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="T36" s="5" t="inlineStr"/>
       <c r="U36" s="4" t="inlineStr">
         <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="X36" s="4" t="inlineStr">
+        <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="V36" s="4" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="W36" s="4" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="X36" s="4" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
       <c r="Y36" s="4" t="inlineStr">
         <is>
           <t>20%</t>
@@ -4952,7 +4937,7 @@
       </c>
       <c r="Z36" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="AA36" s="4" t="inlineStr">
@@ -4964,10 +4949,11 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (UAE Official Legislation) (Domain uaelegislation.gov.ae registered under United Arab Emirates)
-4. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UAE Official Legislation)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UAE Official Legislation (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: '')
+5. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UAE Official Legislation)
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UAE Official Legislation (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -5002,7 +4988,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Climate &amp; Emissions Disclosure</t>
+          <t>Sustainable Finance &amp; Green Bonds</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -5022,7 +5008,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>LIVE</t>
+          <t>PDF_VALID</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
@@ -5052,7 +5038,7 @@
       <c r="T37" s="5" t="inlineStr"/>
       <c r="U37" s="4" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="V37" s="4" t="inlineStr">
@@ -5089,10 +5075,12 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
-2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of the UAE (CBUAE)) (Domain rulebook.centralbank.ae registered under United Arab Emirates)
-4. (Identity): Regulatory identity: Principles for Sustainability-Related Disclosures | CBUAE Rulebook (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Central Bank of the UAE (CBUAE))
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of the UAE (CBUAE) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Principles for Sustainability-Related Disclosures | CBUAE Rulebook')
+5. (Browser): Discovered underlying PDF: https://www.centralbank.ae/media/ivfkvbak/cbuae-code-of-conduct-blue-en-r5-5-pdf_2021.pdf (Magic %PDF- bytes verified.)
+6. (Identity): Regulatory identity: Principles for Sustainability-Related Disclosures | CBUAE Rulebook (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Central Bank of the UAE (CBUAE))
+7. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of the UAE (CBUAE) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -5340,9 +5328,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Environment Act 2021')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Environment Act 2021')
 5. (Identity): Regulatory identity: Environment Act 2021 (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -5466,9 +5454,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022')
 5. (Identity): Regulatory identity: The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022 (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -5495,12 +5483,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Rules / Measures</t>
+          <t>Regulation</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -5525,7 +5513,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>PDF_VALID</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
@@ -5541,7 +5529,7 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>CONSULTATION</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
@@ -5571,7 +5559,7 @@
       </c>
       <c r="U41" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="V41" s="4" t="inlineStr">
@@ -5586,7 +5574,7 @@
       </c>
       <c r="X41" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="Y41" s="4" t="inlineStr">
@@ -5596,7 +5584,7 @@
       </c>
       <c r="Z41" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="AA41" s="4" t="inlineStr">
@@ -5608,11 +5596,12 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)
+2. (Technical): HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission (SEC)) (Domain www.sec.gov registered under United States)
-4. (Identity): Regulatory identity: UNKNOWN (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission (SEC))
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Commission (SEC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)
-6. (Discovery): Replacement candidate identified: https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors (Candidate title: 'SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)', Verified: False)</t>
+4. (Document): PDF document verified with magic bytes %PDF- (Pages: 885, Text length: 5000)
+5. (Identity): Regulatory identity: Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission (SEC))
+6. (Currentness): Lifecycle: CONSULTATION (Document is a consultation paper or draft proposal, not a final binding regulation.) (Issuing authority verified as authoritative: Securities and Exchange Commission (SEC) (TIER_1_PRIMARY_REGULATOR); Document contains draft/consultation markers; not a final regulation.)
+7. (Discovery): Replacement candidate identified: https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors (Candidate title: 'SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)', Verified: False)</t>
         </is>
       </c>
     </row>
@@ -5734,9 +5723,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)
+2. (Technical): HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Department of Labor (DOL / EBSA)) (Domain www.dol.gov registered under United States)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor')
 5. (Identity): Regulatory identity: US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Department of Labor (DOL / EBSA))
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Department of Labor (DOL / EBSA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -6283,7 +6272,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>www.cac.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -6308,19 +6297,15 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf?__cf_chl_rt_tk=Axdvxgy90YyoPQs9s1pkU0U9quWDIUu_H2.LiKYEOLI-1789972686-1.0.1.1-l59Xcln1L9iaJ0ypcLn8Qy.6DMej0wc9jScIqHewqVk</t>
+          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>Just a moment...</t>
-        </is>
-      </c>
+          <t>CONNECTION_ERROR</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
           <t>Corporate Affairs Commission (CAC)</t>
@@ -6341,30 +6326,30 @@
       <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="5" t="inlineStr">
         <is>
-          <t>NONE_FOUND</t>
+          <t>NO_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="T47" s="5" t="inlineStr"/>
       <c r="U47" s="4" t="inlineStr">
         <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="X47" s="4" t="inlineStr">
+        <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="V47" s="4" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="W47" s="4" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="X47" s="4" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
       <c r="Y47" s="4" t="inlineStr">
         <is>
           <t>20%</t>
@@ -6372,7 +6357,7 @@
       </c>
       <c r="Z47" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="AA47" s="4" t="inlineStr">
@@ -6384,11 +6369,10 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP None (CONNECTION_ERROR) (Content-Type: , Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)
-4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
-5. (Identity): Regulatory identity: www.cac.gov.ng (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))
+5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -6707,12 +6691,12 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>https://www.cbn.gov.ng/out/2012/ccd/circular-nsbp.pdf?__cf_chl_rt_tk=itnpNabUomo2e5NcA2X8aLw3TWEHbQBtVtJZ4HljY4o-1789972710-1.0.1.1-VvT77lz_ClxERYksjq3uERgmeT7sz3Usn0sAjKusM0Q</t>
+          <t>https://www.cbn.gov.ng/out/2012/ccd/circular-nsbp.pdf?__cf_chl_rt_tk=SafPVnuA4C0xdj9Om2UewRZNlCHcZP3L3SHDN0tz3K8-1789975702-1.0.1.1-.FisoWRs0Ofi.MLW2JFwkwWsRQuubw.6jhiup6vHNqg</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>BOT_PROTECTION</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -6783,7 +6767,7 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of Nigeria (CBN)) (Domain www.cbn.gov.ng registered under Nigeria)
 4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
 5. (Identity): Regulatory identity: www.cbn.gov.ng (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Central Bank of Nigeria (CBN))
@@ -6979,55 +6963,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7039,7 +7022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E283"/>
+  <dimension ref="A1:E287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7529,7 +7512,7 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8004,7 +7987,7 @@
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8037,7 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex')</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8102,7 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -8144,7 +8127,7 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -8154,7 +8137,7 @@
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8152,7 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -8194,17 +8177,17 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Delegated regulation - EU - 2023/2772 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8219,17 +8202,17 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Delegated regulation - EU - 2023/2772 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Large Enterprises / PIEs, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
@@ -8244,23 +8227,23 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng (Candidate title: 'Commission Delegated Regulation (EU) 2023/2772 (ESRS Set 1)', Verified: False)</t>
+          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
@@ -8269,17 +8252,17 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>EN EN - o n a v o l u n t a r y s u s</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Replacement candidate identified: https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng (Candidate title: 'Commission Delegated Regulation (EU) 2023/2772 (ESRS Set 1)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -8299,12 +8282,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://ec.europa.eu/finance/docs/law/250730-recommendation-vsme_en.pdf (Redirect chain length: 1)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8312,7 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Redirect detected (healthy_redirect) to: https://ec.europa.eu/finance/docs/law/250730-recommendation-vsme_en.pdf (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
@@ -8349,12 +8332,12 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (European Commission) (Domain ec.europa.eu registered under European Union)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8374,12 +8357,12 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 8, Text length: 5000)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (European Commission) (Domain ec.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8382,12 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: EN EN - o n a v o l u n t a r y s u s (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: European Commission)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 8, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -8424,18 +8407,18 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: European Commission (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: EN EN - o n a v o l u n t a r y s u s (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: European Commission)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
@@ -8444,17 +8427,17 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex</t>
+          <t>EN EN - o n a v o l u n t a r y s u s</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: European Commission (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8457,12 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8482,12 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8524,12 +8507,12 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8532,12 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8574,18 +8557,18 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+          <t>Regulatory identity: EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
@@ -8594,17 +8577,17 @@
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>Search results - EUR-Lex</t>
+          <t>EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8607,12 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8649,12 +8632,12 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8674,12 +8657,12 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8682,12 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Search results - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8724,18 +8707,18 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Search results - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
@@ -8744,17 +8727,17 @@
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8757,12 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8799,12 +8782,12 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8824,12 +8807,12 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8849,12 +8832,12 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex (Consultation / Draft) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8874,18 +8857,18 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex (Consultation / Draft) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
@@ -8894,17 +8877,17 @@
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -8919,17 +8902,17 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8944,17 +8927,17 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8952,17 @@
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8994,23 +8977,23 @@
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
@@ -9019,23 +9002,23 @@
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Regulatory identity: EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
@@ -9044,17 +9027,17 @@
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9057,12 @@
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -9099,12 +9082,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex')</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9124,12 +9107,12 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -9149,18 +9132,18 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
@@ -9169,23 +9152,23 @@
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>Search results - EUR-Lex</t>
+          <t>EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Regulatory identity: EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
@@ -9194,17 +9177,17 @@
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>Search results - EUR-Lex</t>
+          <t>EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9207,12 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -9249,12 +9232,12 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9274,12 +9257,12 @@
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -9299,18 +9282,18 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: SUPERSEDED (Document explicitly superseded/repealed) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
@@ -9324,18 +9307,18 @@
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
@@ -9349,12 +9332,12 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Lifecycle: SUPERSEDED (Document explicitly superseded/repealed) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed)</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9357,12 @@
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -9399,12 +9382,12 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9424,12 +9407,12 @@
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -9449,18 +9432,18 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
@@ -9469,23 +9452,23 @@
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
@@ -9494,17 +9477,17 @@
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -9519,17 +9502,17 @@
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -9544,17 +9527,17 @@
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9569,92 +9552,92 @@
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>European Union</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>Business responsibility and sustainability reporting by listed entities</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>European Union</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>Business responsibility and sustainability reporting by listed entities</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Regulatory identity: Search results - EUR-Lex (Delegated Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>European Union</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>Business responsibility and sustainability reporting by listed entities</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Board of India (SEBI)) (Domain www.sebi.gov.in registered under India)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9657,12 @@
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Business responsibility and sustainability reporting by listed entities (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Securities and Exchange Board of India (SEBI))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
         </is>
       </c>
     </row>
@@ -9699,18 +9682,18 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Board of India (SEBI) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
@@ -9719,23 +9702,23 @@
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>Error page</t>
+          <t>Business responsibility and sustainability reporting by listed entities</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Board of India (SEBI)) (Domain www.sebi.gov.in registered under India)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
@@ -9744,23 +9727,23 @@
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>Error page</t>
+          <t>Business responsibility and sustainability reporting by listed entities</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Regulatory identity: Business responsibility and sustainability reporting by listed entities (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Securities and Exchange Board of India (SEBI))</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
@@ -9769,17 +9752,17 @@
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>Error page</t>
+          <t>Business responsibility and sustainability reporting by listed entities</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Corporate Affairs (MCA)) (Domain www.mca.gov.in registered under India)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Board of India (SEBI) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -9794,17 +9777,17 @@
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>Error page</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Error page')</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
         </is>
       </c>
     </row>
@@ -9819,17 +9802,17 @@
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>Error page</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Error page (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Ministry of Corporate Affairs (MCA))</t>
+          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9844,23 +9827,23 @@
       </c>
       <c r="C113" s="13" t="inlineStr">
         <is>
-          <t>Error page</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Corporate Affairs (MCA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Corporate Affairs (MCA)) (Domain www.mca.gov.in registered under India)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
@@ -9869,23 +9852,23 @@
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'HOME')</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
@@ -9894,23 +9877,23 @@
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
+          <t>Regulatory identity: HOME (Act / Legislation) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Ministry of Corporate Affairs (MCA))</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
@@ -9919,17 +9902,17 @@
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Reserve Bank of India (RBI)) (Domain www.rbi.org.in registered under India)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Corporate Affairs (MCA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9932,12 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Notifications (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Reserve Bank of India (RBI))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
         </is>
       </c>
     </row>
@@ -9974,87 +9957,87 @@
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Reserve Bank of India (RBI) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>Kingdom of Saudi Arabia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>ESG Disclosure Guidelines</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Kingdom of Saudi Arabia' (Exact match with target jurisdiction: 'Kingdom of Saudi Arabia')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Reserve Bank of India (RBI)) (Domain www.rbi.org.in registered under India)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>Kingdom of Saudi Arabia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>ESG Disclosure Guidelines</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Regulatory identity: Notifications (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Reserve Bank of India (RBI))</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>Kingdom of Saudi Arabia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>ESG Disclosure Guidelines</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (sseinitiative.org) (Domain sseinitiative.org registered under Kingdom of Saudi Arabia)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Reserve Bank of India (RBI) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10057,12 @@
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 30, Text length: 5000)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Kingdom of Saudi Arabia' (Exact match with target jurisdiction: 'Kingdom of Saudi Arabia')</t>
         </is>
       </c>
     </row>
@@ -10099,12 +10082,12 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: ESG Disclosure Guidelines (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10124,87 +10107,87 @@
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (sseinitiative.org) (Domain sseinitiative.org registered under Kingdom of Saudi Arabia)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kingdom of Saudi Arabia</t>
         </is>
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>ESG Reporting Guide</t>
+          <t>ESG Disclosure Guidelines</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Kuwait' (Exact match with target jurisdiction: 'Kuwait')</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 30, Text length: 5000)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kingdom of Saudi Arabia</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>ESG Reporting Guide</t>
+          <t>ESG Disclosure Guidelines</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Regulatory identity: ESG Disclosure Guidelines (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kingdom of Saudi Arabia</t>
         </is>
       </c>
       <c r="C127" s="13" t="inlineStr">
         <is>
-          <t>ESG Reporting Guide</t>
+          <t>ESG Disclosure Guidelines</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Boursa Kuwait) (Domain www.boursakuwait.com.kw registered under Kuwait)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10224,12 +10207,12 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'ESG Reporting Guide')</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Kuwait' (Exact match with target jurisdiction: 'Kuwait')</t>
         </is>
       </c>
     </row>
@@ -10249,12 +10232,12 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: ESG Reporting Guide (Guideline / Standard) (Topic: Corporate Governance &amp; CSR, Population: Listed Companies / Issuers, Authority: Boursa Kuwait)</t>
+          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10274,87 +10257,87 @@
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Boursa Kuwait (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Boursa Kuwait) (Domain www.boursakuwait.com.kw registered under Kuwait)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
+          <t>ESG Reporting Guide</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Oman' (Exact match with target jurisdiction: 'Oman')</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'ESG Reporting Guide')</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
+          <t>ESG Reporting Guide</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Regulatory identity: ESG Reporting Guide (Guideline / Standard) (Topic: Corporate Governance &amp; CSR, Population: Listed Companies / Issuers, Authority: Boursa Kuwait)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
+          <t>ESG Reporting Guide</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Muscat Stock Exchange (MSX)) (Domain www.msx.om registered under Oman)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Boursa Kuwait (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10374,12 +10357,12 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 18, Text length: 5000)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Oman' (Exact match with target jurisdiction: 'Oman')</t>
         </is>
       </c>
     </row>
@@ -10399,12 +10382,12 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: His Majesty Sultan Haitham bin Tariq - -God bless him- (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: All Commercial Enterprises, Authority: Muscat Stock Exchange (MSX))</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10424,87 +10407,87 @@
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Muscat Stock Exchange (MSX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Muscat Stock Exchange (MSX)) (Domain www.msx.om registered under Oman)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>ESG Initiative</t>
+          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Qatar' (Exact match with target jurisdiction: 'Qatar')</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 18, Text length: 5000)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>ESG Initiative</t>
+          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html;charset=UTF-8, Latency: 0ms)</t>
+          <t>Regulatory identity: His Majesty Sultan Haitham bin Tariq - -God bless him- (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: All Commercial Enterprises, Authority: Muscat Stock Exchange (MSX))</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>ESG Initiative</t>
+          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Qatar Stock Exchange (QSE)) (Domain www.qe.com.qa registered under Qatar)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Muscat Stock Exchange (MSX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10524,12 +10507,12 @@
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: ESG Initiative (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Qatar Stock Exchange (QSE))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Qatar' (Exact match with target jurisdiction: 'Qatar')</t>
         </is>
       </c>
     </row>
@@ -10549,87 +10532,87 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Qatar Stock Exchange (QSE) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html;charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
+          <t>ESG Initiative</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Qatar Stock Exchange (QSE)) (Domain www.qe.com.qa registered under Qatar)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
+          <t>ESG Initiative</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Regulatory identity: ESG Initiative (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Qatar Stock Exchange (QSE))</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
+          <t>ESG Initiative</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Singapore Exchange (SGX Group)) (Domain rulebook.sgx.com registered under Singapore)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Qatar Stock Exchange (QSE) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10649,12 +10632,12 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Practice Note 7.6 Sustainability Reporting Guide | Rulebooks (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Singapore Exchange (SGX Group))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
         </is>
       </c>
     </row>
@@ -10674,18 +10657,18 @@
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Singapore Exchange (SGX Group) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
@@ -10694,23 +10677,23 @@
       </c>
       <c r="C147" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Singapore Exchange (SGX Group)) (Domain rulebook.sgx.com registered under Singapore)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
@@ -10719,23 +10702,23 @@
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://www.mas.gov.sg/Custom/errorpages/PageNotFound.aspx (Redirect chain length: 1)</t>
+          <t>Regulatory identity: Practice Note 7.6 Sustainability Reporting Guide | Rulebooks (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Singapore Exchange (SGX Group))</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
@@ -10744,17 +10727,17 @@
       </c>
       <c r="C149" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>HTTP 404 (HTTP_404) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Singapore Exchange (SGX Group) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10769,17 +10752,17 @@
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
         </is>
       </c>
     </row>
@@ -10794,17 +10777,17 @@
       </c>
       <c r="C151" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10819,17 +10802,17 @@
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
         </is>
       </c>
     </row>
@@ -10844,23 +10827,23 @@
       </c>
       <c r="C153" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://www.mas.gov.sg/regulation/guidelines/guidelines-on-environmental-risk-management (Candidate title: 'Monetary Authority of Singapore (MAS) Guidelines on Environmental Risk Management', Verified: True)</t>
+          <t>Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
@@ -10869,17 +10852,17 @@
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>Guidelines on Environmental Risk Management for Asset Managers</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10894,17 +10877,17 @@
       </c>
       <c r="C155" s="13" t="inlineStr">
         <is>
-          <t>Guidelines on Environmental Risk Management for Asset Managers</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
         </is>
       </c>
     </row>
@@ -10919,17 +10902,17 @@
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>Guidelines on Environmental Risk Management for Asset Managers</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10944,17 +10927,17 @@
       </c>
       <c r="C157" s="13" t="inlineStr">
         <is>
-          <t>Guidelines on Environmental Risk Management for Asset Managers</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Guidelines on Environmental Risk Management for Asset Managers (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Financial Institutions / Asset Managers, Authority: Monetary Authority of Singapore (MAS))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
         </is>
       </c>
     </row>
@@ -10969,23 +10952,23 @@
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>Guidelines on Environmental Risk Management for Asset Managers</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Maintenance (Regulation) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
@@ -10994,17 +10977,17 @@
       </c>
       <c r="C159" s="13" t="inlineStr">
         <is>
-          <t>Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11019,17 +11002,17 @@
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
         </is>
       </c>
     </row>
@@ -11044,17 +11027,17 @@
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11069,17 +11052,17 @@
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
         </is>
       </c>
     </row>
@@ -11094,42 +11077,42 @@
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental,</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11149,12 +11132,12 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11174,12 +11157,12 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Abu Dhabi Securities Exchange (ADX)) (Domain www.adx.ae registered under United Arab Emirates)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11199,12 +11182,12 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 40, Text length: 5000)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Abu Dhabi Securities Exchange (ADX)) (Domain www.adx.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11224,12 +11207,12 @@
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental, (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Abu Dhabi Securities Exchange (ADX))</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 40, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -11249,18 +11232,18 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Abu Dhabi Securities Exchange (ADX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental, (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Abu Dhabi Securities Exchange (ADX))</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
@@ -11269,17 +11252,17 @@
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental,</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Abu Dhabi Securities Exchange (ADX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11299,12 +11282,12 @@
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://adxservices.adx.ae/webservices/dataservices/error.html?aspxerrorpath=/WebServices/DataServices/contentDownload.aspx (Redirect chain length: 1)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11312,7 @@
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Redirect detected (healthy_redirect) to: https://adxservices.adx.ae/webservices/dataservices/error.html?aspxerrorpath=/WebServices/DataServices/contentDownload.aspx (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11332,12 @@
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Abu Dhabi Securities Exchange (ADX)) (Domain adxservices.adx.ae registered under United Arab Emirates)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11374,12 +11357,12 @@
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Abu Dhabi Securities Exchange (ADX))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Abu Dhabi Securities Exchange (ADX)) (Domain adxservices.adx.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11399,18 +11382,18 @@
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Abu Dhabi Securities Exchange (ADX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Abu Dhabi Securities Exchange (ADX))</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
@@ -11424,12 +11407,12 @@
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Abu Dhabi Securities Exchange (ADX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11449,12 +11432,12 @@
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11474,12 +11457,12 @@
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.ecgi.global) (Domain www.ecgi.global registered under United Arab Emirates)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11499,12 +11482,12 @@
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 0, Text length: 0)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.ecgi.global) (Domain www.ecgi.global registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11507,12 @@
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 0, Text length: 0)</t>
         </is>
       </c>
     </row>
@@ -11549,12 +11532,12 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
@@ -11574,18 +11557,18 @@
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://www.sca.gov.ae/en/regulations/regulations-listing.aspx (Candidate title: 'SCA Regulations Listing Portal (UAE)', Verified: True)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
@@ -11594,17 +11577,17 @@
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Replacement candidate identified: https://www.sca.gov.ae/en/regulations/regulations-listing.aspx (Candidate title: 'SCA Regulations Listing Portal (UAE)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -11624,12 +11607,12 @@
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (moderate_redirect) to: https://www.uaecma.gov.ae/en/home (Redirect chain length: 4)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11637,7 @@
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
+          <t>Redirect detected (moderate_redirect) to: https://www.uaecma.gov.ae/en/home (Redirect chain length: 4)</t>
         </is>
       </c>
     </row>
@@ -11674,12 +11657,12 @@
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (www.uaecma.gov.ae) (Domain www.uaecma.gov.ae registered under United Arab Emirates)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11699,12 +11682,12 @@
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Services (Consultation / Draft) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (www.uaecma.gov.ae) (Domain www.uaecma.gov.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11724,18 +11707,18 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Services (Consultation / Draft) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
@@ -11744,17 +11727,17 @@
       </c>
       <c r="C189" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11774,12 +11757,12 @@
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11799,12 +11782,12 @@
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UAE Official Legislation) (Domain uaelegislation.gov.ae registered under United Arab Emirates)</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11824,12 +11807,12 @@
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UAE Official Legislation)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UAE Official Legislation) (Domain uaelegislation.gov.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11849,18 +11832,18 @@
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UAE Official Legislation (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: '')</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
@@ -11869,23 +11852,23 @@
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UAE Official Legislation)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
@@ -11894,17 +11877,17 @@
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UAE Official Legislation (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11924,12 +11907,12 @@
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of the UAE (CBUAE)) (Domain rulebook.centralbank.ae registered under United Arab Emirates)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11949,12 +11932,12 @@
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Principles for Sustainability-Related Disclosures | CBUAE Rulebook (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Central Bank of the UAE (CBUAE))</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11974,112 +11957,112 @@
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of the UAE (CBUAE) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of the UAE (CBUAE)) (Domain rulebook.centralbank.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B199" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C199" s="13" t="inlineStr">
         <is>
-          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
+          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Principles for Sustainability-Related Disclosures | CBUAE Rulebook')</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C200" s="13" t="inlineStr">
         <is>
-          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
+          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Discovered underlying PDF: https://www.centralbank.ae/media/ivfkvbak/cbuae-code-of-conduct-blue-en-r5-5-pdf_2021.pdf (Magic %PDF- bytes verified.)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C201" s="13" t="inlineStr">
         <is>
-          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
+          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Government (BEIS / DESNZ / Cabinet Office)) (Domain assets.publishing.service.gov.uk registered under United Kingdom)</t>
+          <t>Regulatory identity: Principles for Sustainability-Related Disclosures | CBUAE Rulebook (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Central Bank of the UAE (CBUAE))</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C202" s="13" t="inlineStr">
         <is>
-          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
+          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 23, Text length: 5000)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of the UAE (CBUAE) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12099,12 +12082,12 @@
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Government (BEIS / DESNZ / Cabinet Office))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
         </is>
       </c>
     </row>
@@ -12124,18 +12107,18 @@
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Government (BEIS / DESNZ / Cabinet Office) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
@@ -12144,23 +12127,23 @@
       </c>
       <c r="C205" s="13" t="inlineStr">
         <is>
-          <t>Environment Act 2021</t>
+          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Government (BEIS / DESNZ / Cabinet Office)) (Domain assets.publishing.service.gov.uk registered under United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
@@ -12169,23 +12152,23 @@
       </c>
       <c r="C206" s="13" t="inlineStr">
         <is>
-          <t>Environment Act 2021</t>
+          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 23, Text length: 5000)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
@@ -12194,23 +12177,23 @@
       </c>
       <c r="C207" s="13" t="inlineStr">
         <is>
-          <t>Environment Act 2021</t>
+          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)</t>
+          <t>Regulatory identity: Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Government (BEIS / DESNZ / Cabinet Office))</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
@@ -12219,17 +12202,17 @@
       </c>
       <c r="C208" s="13" t="inlineStr">
         <is>
-          <t>Environment Act 2021</t>
+          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Environment Act 2021')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Government (BEIS / DESNZ / Cabinet Office) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12249,12 +12232,12 @@
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Environment Act 2021 (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
         </is>
       </c>
     </row>
@@ -12274,18 +12257,18 @@
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
@@ -12294,23 +12277,23 @@
       </c>
       <c r="C211" s="13" t="inlineStr">
         <is>
-          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
+          <t>Environment Act 2021</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
@@ -12319,23 +12302,23 @@
       </c>
       <c r="C212" s="13" t="inlineStr">
         <is>
-          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
+          <t>Environment Act 2021</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Environment Act 2021')</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
@@ -12344,23 +12327,23 @@
       </c>
       <c r="C213" s="13" t="inlineStr">
         <is>
-          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
+          <t>Environment Act 2021</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)</t>
+          <t>Regulatory identity: Environment Act 2021 (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
@@ -12369,17 +12352,17 @@
       </c>
       <c r="C214" s="13" t="inlineStr">
         <is>
-          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
+          <t>Environment Act 2021</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12399,12 +12382,12 @@
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022 (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
         </is>
       </c>
     </row>
@@ -12424,112 +12407,112 @@
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B217" s="13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C217" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E217" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C218" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
         </is>
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022')</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C219" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E219" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission (SEC)) (Domain www.sec.gov registered under United States)</t>
+          <t>Regulatory identity: The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022 (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C220" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission (SEC))</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12544,17 +12527,17 @@
       </c>
       <c r="C221" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E221" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Commission (SEC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
         </is>
       </c>
     </row>
@@ -12569,23 +12552,23 @@
       </c>
       <c r="C222" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors (Candidate title: 'SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)', Verified: False)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B223" s="13" t="inlineStr">
         <is>
@@ -12594,23 +12577,23 @@
       </c>
       <c r="C223" s="13" t="inlineStr">
         <is>
-          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E223" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission (SEC)) (Domain www.sec.gov registered under United States)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
@@ -12619,23 +12602,23 @@
       </c>
       <c r="C224" s="13" t="inlineStr">
         <is>
-          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 885, Text length: 5000)</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B225" s="13" t="inlineStr">
         <is>
@@ -12644,23 +12627,23 @@
       </c>
       <c r="C225" s="13" t="inlineStr">
         <is>
-          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E225" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Department of Labor (DOL / EBSA)) (Domain www.dol.gov registered under United States)</t>
+          <t>Regulatory identity: Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission (SEC))</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
@@ -12669,23 +12652,23 @@
       </c>
       <c r="C226" s="13" t="inlineStr">
         <is>
-          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor')</t>
+          <t>Lifecycle: CONSULTATION (Document is a consultation paper or draft proposal, not a final binding regulation.) (Issuing authority verified as authoritative: Securities and Exchange Commission (SEC) (TIER_1_PRIMARY_REGULATOR); Document contains draft/consultation markers; not a final regulation.)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B227" s="13" t="inlineStr">
         <is>
@@ -12694,17 +12677,17 @@
       </c>
       <c r="C227" s="13" t="inlineStr">
         <is>
-          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E227" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Department of Labor (DOL / EBSA))</t>
+          <t>Replacement candidate identified: https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors (Candidate title: 'SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)', Verified: False)</t>
         </is>
       </c>
     </row>
@@ -12724,18 +12707,18 @@
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Department of Labor (DOL / EBSA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B229" s="13" t="inlineStr">
         <is>
@@ -12744,23 +12727,23 @@
       </c>
       <c r="C229" s="13" t="inlineStr">
         <is>
-          <t>Bill Text</t>
+          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E229" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
+          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
@@ -12769,23 +12752,23 @@
       </c>
       <c r="C230" s="13" t="inlineStr">
         <is>
-          <t>Bill Text</t>
+          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Department of Labor (DOL / EBSA)) (Domain www.dol.gov registered under United States)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B231" s="13" t="inlineStr">
         <is>
@@ -12794,23 +12777,23 @@
       </c>
       <c r="C231" s="13" t="inlineStr">
         <is>
-          <t>Bill Text</t>
+          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (California State Legislature) (Domain leginfo.legislature.ca.gov registered under United States)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor')</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B232" s="13" t="inlineStr">
         <is>
@@ -12819,7 +12802,7 @@
       </c>
       <c r="C232" s="13" t="inlineStr">
         <is>
-          <t>Bill Text</t>
+          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
@@ -12829,13 +12812,13 @@
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Bill Text (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: California State Legislature)</t>
+          <t>Regulatory identity: US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Department of Labor (DOL / EBSA))</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B233" s="13" t="inlineStr">
         <is>
@@ -12844,7 +12827,7 @@
       </c>
       <c r="C233" s="13" t="inlineStr">
         <is>
-          <t>Bill Text</t>
+          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
@@ -12854,22 +12837,22 @@
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: California State Legislature (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Department of Labor (DOL / EBSA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C234" s="13" t="inlineStr">
         <is>
-          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
+          <t>Bill Text</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
@@ -12879,22 +12862,22 @@
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B235" s="13" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C235" s="13" t="inlineStr">
         <is>
-          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
+          <t>Bill Text</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
@@ -12904,22 +12887,22 @@
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B236" s="13" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C236" s="13" t="inlineStr">
         <is>
-          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
+          <t>Bill Text</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
@@ -12929,57 +12912,57 @@
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (California State Legislature) (Domain leginfo.legislature.ca.gov registered under United States)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B237" s="13" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C237" s="13" t="inlineStr">
         <is>
-          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
+          <t>Bill Text</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 22, Text length: 5000)</t>
+          <t>Regulatory identity: Bill Text (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: California State Legislature)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B238" s="13" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C238" s="13" t="inlineStr">
         <is>
-          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
+          <t>Bill Text</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: California State Legislature (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12999,18 +12982,18 @@
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B240" s="13" t="inlineStr">
         <is>
@@ -13019,23 +13002,23 @@
       </c>
       <c r="C240" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B241" s="13" t="inlineStr">
         <is>
@@ -13044,23 +13027,23 @@
       </c>
       <c r="C241" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
@@ -13069,23 +13052,23 @@
       </c>
       <c r="C242" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 22, Text length: 5000)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B243" s="13" t="inlineStr">
         <is>
@@ -13094,23 +13077,23 @@
       </c>
       <c r="C243" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 8, Text length: 0)</t>
+          <t>Regulatory identity: FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B244" s="13" t="inlineStr">
         <is>
@@ -13119,17 +13102,17 @@
       </c>
       <c r="C244" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -13149,18 +13132,18 @@
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B246" s="13" t="inlineStr">
         <is>
@@ -13169,23 +13152,23 @@
       </c>
       <c r="C246" s="13" t="inlineStr">
         <is>
-          <t>Environmental Impact Assessment Act</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B247" s="13" t="inlineStr">
         <is>
@@ -13194,23 +13177,23 @@
       </c>
       <c r="C247" s="13" t="inlineStr">
         <is>
-          <t>Environmental Impact Assessment Act</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://www.policyvault.africa/policy/environmental-impact-assessment-act-2/ (Redirect chain length: 1)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B248" s="13" t="inlineStr">
         <is>
@@ -13219,23 +13202,23 @@
       </c>
       <c r="C248" s="13" t="inlineStr">
         <is>
-          <t>Environmental Impact Assessment Act</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 8, Text length: 0)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B249" s="13" t="inlineStr">
         <is>
@@ -13244,23 +13227,23 @@
       </c>
       <c r="C249" s="13" t="inlineStr">
         <is>
-          <t>Environmental Impact Assessment Act</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.policyvault.africa) (Domain www.policyvault.africa registered under Nigeria)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
@@ -13269,17 +13252,17 @@
       </c>
       <c r="C250" s="13" t="inlineStr">
         <is>
-          <t>Environmental Impact Assessment Act</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Environmental Impact Assessment Act (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -13299,12 +13282,12 @@
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13324,18 +13307,18 @@
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://nesrea.gov.ng/policies-guidelines/ (Candidate title: 'NESREA Official Environmental Regulations and Guidelines (Nigeria)', Verified: True)</t>
+          <t>Redirect detected (healthy_redirect) to: https://www.policyvault.africa/policy/environmental-impact-assessment-act-2/ (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B253" s="13" t="inlineStr">
         <is>
@@ -13344,23 +13327,23 @@
       </c>
       <c r="C253" s="13" t="inlineStr">
         <is>
-          <t>www.cac.gov.ng</t>
+          <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B254" s="13" t="inlineStr">
         <is>
@@ -13369,23 +13352,23 @@
       </c>
       <c r="C254" s="13" t="inlineStr">
         <is>
-          <t>www.cac.gov.ng</t>
+          <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.policyvault.africa) (Domain www.policyvault.africa registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B255" s="13" t="inlineStr">
         <is>
@@ -13394,23 +13377,23 @@
       </c>
       <c r="C255" s="13" t="inlineStr">
         <is>
-          <t>www.cac.gov.ng</t>
+          <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)</t>
+          <t>Regulatory identity: Environmental Impact Assessment Act (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B256" s="13" t="inlineStr">
         <is>
@@ -13419,23 +13402,23 @@
       </c>
       <c r="C256" s="13" t="inlineStr">
         <is>
-          <t>www.cac.gov.ng</t>
+          <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B257" s="13" t="inlineStr">
         <is>
@@ -13444,17 +13427,17 @@
       </c>
       <c r="C257" s="13" t="inlineStr">
         <is>
-          <t>www.cac.gov.ng</t>
+          <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E257" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: www.cac.gov.ng (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))</t>
+          <t>Replacement candidate identified: https://nesrea.gov.ng/policies-guidelines/ (Candidate title: 'NESREA Official Environmental Regulations and Guidelines (Nigeria)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -13469,23 +13452,23 @@
       </c>
       <c r="C258" s="13" t="inlineStr">
         <is>
-          <t>www.cac.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B259" s="13" t="inlineStr">
         <is>
@@ -13494,23 +13477,23 @@
       </c>
       <c r="C259" s="13" t="inlineStr">
         <is>
-          <t>Policies &amp; Guidelines</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E259" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>HTTP None (CONNECTION_ERROR) (Content-Type: , Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B260" s="13" t="inlineStr">
         <is>
@@ -13519,23 +13502,23 @@
       </c>
       <c r="C260" s="13" t="inlineStr">
         <is>
-          <t>Policies &amp; Guidelines</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://nesrea.gov.ng/policies-guidelines/ (Redirect chain length: 1)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B261" s="13" t="inlineStr">
         <is>
@@ -13544,23 +13527,23 @@
       </c>
       <c r="C261" s="13" t="inlineStr">
         <is>
-          <t>Policies &amp; Guidelines</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
@@ -13569,17 +13552,17 @@
       </c>
       <c r="C262" s="13" t="inlineStr">
         <is>
-          <t>Policies &amp; Guidelines</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -13599,12 +13582,12 @@
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Policies &amp; Guidelines (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13624,18 +13607,18 @@
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Redirect detected (healthy_redirect) to: https://nesrea.gov.ng/policies-guidelines/ (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B265" s="13" t="inlineStr">
         <is>
@@ -13644,23 +13627,23 @@
       </c>
       <c r="C265" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Policies &amp; Guidelines</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B266" s="13" t="inlineStr">
         <is>
@@ -13669,23 +13652,23 @@
       </c>
       <c r="C266" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Policies &amp; Guidelines</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B267" s="13" t="inlineStr">
         <is>
@@ -13694,23 +13677,23 @@
       </c>
       <c r="C267" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Policies &amp; Guidelines</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E267" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (unfccc.int) (Domain unfccc.int registered under Nigeria)</t>
+          <t>Regulatory identity: Policies &amp; Guidelines (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B268" s="13" t="inlineStr">
         <is>
@@ -13719,17 +13702,17 @@
       </c>
       <c r="C268" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Policies &amp; Guidelines</t>
         </is>
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 5, Text length: 0)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -13749,12 +13732,12 @@
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E269" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13774,12 +13757,12 @@
       </c>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -13799,18 +13782,18 @@
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E271" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://unfccc.int/sites/default/files/NDC/2022-06/Nigeria_Updated_NDC_2021.pdf (Candidate title: 'Nigeria Updated NDC 2021', Verified: False)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (unfccc.int) (Domain unfccc.int registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B272" s="13" t="inlineStr">
         <is>
@@ -13819,23 +13802,23 @@
       </c>
       <c r="C272" s="13" t="inlineStr">
         <is>
-          <t>www.cbn.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 5, Text length: 0)</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B273" s="13" t="inlineStr">
         <is>
@@ -13844,23 +13827,23 @@
       </c>
       <c r="C273" s="13" t="inlineStr">
         <is>
-          <t>www.cbn.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E273" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B274" s="13" t="inlineStr">
         <is>
@@ -13869,23 +13852,23 @@
       </c>
       <c r="C274" s="13" t="inlineStr">
         <is>
-          <t>www.cbn.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of Nigeria (CBN)) (Domain www.cbn.gov.ng registered under Nigeria)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B275" s="13" t="inlineStr">
         <is>
@@ -13894,17 +13877,17 @@
       </c>
       <c r="C275" s="13" t="inlineStr">
         <is>
-          <t>www.cbn.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E275" s="13" t="inlineStr">
         <is>
-          <t>Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)</t>
+          <t>Replacement candidate identified: https://unfccc.int/sites/default/files/NDC/2022-06/Nigeria_Updated_NDC_2021.pdf (Candidate title: 'Nigeria Updated NDC 2021', Verified: False)</t>
         </is>
       </c>
     </row>
@@ -13924,12 +13907,12 @@
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: www.cbn.gov.ng (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Central Bank of Nigeria (CBN))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13949,18 +13932,18 @@
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E277" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of Nigeria (CBN) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B278" s="13" t="inlineStr">
         <is>
@@ -13969,23 +13952,23 @@
       </c>
       <c r="C278" s="13" t="inlineStr">
         <is>
-          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+          <t>www.cbn.gov.ng</t>
         </is>
       </c>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of Nigeria (CBN)) (Domain www.cbn.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B279" s="13" t="inlineStr">
         <is>
@@ -13994,23 +13977,23 @@
       </c>
       <c r="C279" s="13" t="inlineStr">
         <is>
-          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+          <t>www.cbn.gov.ng</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E279" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B280" s="13" t="inlineStr">
         <is>
@@ -14019,23 +14002,23 @@
       </c>
       <c r="C280" s="13" t="inlineStr">
         <is>
-          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+          <t>www.cbn.gov.ng</t>
         </is>
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission Nigeria (SEC NG)) (Domain sec.gov.ng registered under Nigeria)</t>
+          <t>Regulatory identity: www.cbn.gov.ng (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Central Bank of Nigeria (CBN))</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B281" s="13" t="inlineStr">
         <is>
@@ -14044,17 +14027,17 @@
       </c>
       <c r="C281" s="13" t="inlineStr">
         <is>
-          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+          <t>www.cbn.gov.ng</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E281" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 12, Text length: 5000)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of Nigeria (CBN) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -14074,12 +14057,12 @@
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission Nigeria (SEC NG))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -14099,10 +14082,110 @@
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="E283" s="13" t="inlineStr">
+        <is>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B284" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C284" s="13" t="inlineStr">
+        <is>
+          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+        </is>
+      </c>
+      <c r="D284" s="12" t="inlineStr">
+        <is>
+          <t>AUTHORITY</t>
+        </is>
+      </c>
+      <c r="E284" s="13" t="inlineStr">
+        <is>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission Nigeria (SEC NG)) (Domain sec.gov.ng registered under Nigeria)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B285" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C285" s="13" t="inlineStr">
+        <is>
+          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+        </is>
+      </c>
+      <c r="D285" s="12" t="inlineStr">
+        <is>
+          <t>DOCUMENT</t>
+        </is>
+      </c>
+      <c r="E285" s="13" t="inlineStr">
+        <is>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 12, Text length: 5000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B286" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C286" s="13" t="inlineStr">
+        <is>
+          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+        </is>
+      </c>
+      <c r="D286" s="12" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="E286" s="13" t="inlineStr">
+        <is>
+          <t>Regulatory identity: NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission Nigeria (SEC NG))</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B287" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C287" s="13" t="inlineStr">
+        <is>
+          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+        </is>
+      </c>
+      <c r="D287" s="12" t="inlineStr">
+        <is>
           <t>CURRENTNESS</t>
         </is>
       </c>
-      <c r="E283" s="13" t="inlineStr">
+      <c r="E287" s="13" t="inlineStr">
         <is>
           <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Commission Nigeria (SEC NG) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -14122,7 +14205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14275,7 +14358,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -14295,7 +14378,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>CANDIDATE_UNVERIFIED</t>
+          <t>REPLACEMENT_VERIFIED</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -14306,11 +14389,11 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -14320,17 +14403,17 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>https://www.mas.gov.sg/regulation/guidelines/guidelines-on-environmental-risk-management</t>
+          <t>https://www.sca.gov.ae/en/regulations/regulations-listing.aspx</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Monetary Authority of Singapore (MAS) Guidelines on Environmental Risk Management</t>
+          <t>SCA Regulations Listing Portal (UAE)</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -14346,36 +14429,36 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>https://www.sca.gov.ae/en/regulations/regulations-listing.aspx</t>
+          <t>https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>SCA Regulations Listing Portal (UAE)</t>
+          <t>SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>REPLACEMENT_VERIFIED</t>
+          <t>CANDIDATE_UNVERIFIED</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -14386,36 +14469,36 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors</t>
+          <t>https://nesrea.gov.ng/policies-guidelines/</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)</t>
+          <t>NESREA Official Environmental Regulations and Guidelines (Nigeria)</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>CANDIDATE_UNVERIFIED</t>
+          <t>REPLACEMENT_VERIFIED</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -14426,7 +14509,7 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -14435,17 +14518,17 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Environmental Impact Assessment Act</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>https://nesrea.gov.ng/policies-guidelines/</t>
+          <t>https://unfccc.int/sites/default/files/NDC/2022-06/Nigeria_Updated_NDC_2021.pdf</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>NESREA Official Environmental Regulations and Guidelines (Nigeria)</t>
+          <t>Nigeria Updated NDC 2021</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -14455,50 +14538,10 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>REPLACEMENT_VERIFIED</t>
+          <t>CANDIDATE_UNVERIFIED</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>REPLACEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>https://unfccc.int/sites/default/files/NDC/2022-06/Nigeria_Updated_NDC_2021.pdf</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Nigeria Updated NDC 2021</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>CANDIDATE_UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>REPLACEMENT</t>
         </is>
@@ -14754,10 +14797,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>0</v>
@@ -14775,13 +14818,13 @@
         <v>0</v>
       </c>
       <c r="J5" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5" s="16" t="n">
         <v>0</v>
@@ -14790,13 +14833,13 @@
         <v>0</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="16" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -14977,7 +15020,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>0</v>
@@ -15139,13 +15182,13 @@
         <v>4</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="16" t="n">
         <v>4</v>
@@ -15175,13 +15218,13 @@
         <v>0</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -15194,10 +15237,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>0</v>
@@ -15304,10 +15347,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>0</v>
@@ -15328,10 +15371,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" s="16" t="n">
         <v>0</v>
@@ -15363,7 +15406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15603,7 +15646,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>BOT_PROTECTION</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -15625,7 +15668,7 @@
         <is>
           <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.greenfinanceplatform.org) (Domain www.greenfinanceplatform.org registered under China)
 4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
 5. (Identity): Regulatory identity: www.greenfinanceplatform.org (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UNKNOWN)
@@ -15779,9 +15822,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex')
 5. (Identity): Regulatory identity: EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: SUPERSEDED (Document explicitly superseded/repealed by the following: ‘(5) “net turnover” means the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed by the following: ‘(5) “net turnover” means the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover)</t>
         </is>
@@ -15798,17 +15841,17 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>EN EN - o n a v o l u n t a r y s u s</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:32023DC0012https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng</t>
+          <t>http://ec.europa.eu/finance/docs/law/250730-recommendation-vsme_en.pdf</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>PDF_VALID</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -15818,66 +15861,15 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>Access Blocked / Bot Challenge Unresolved</t>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Identity): Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)
-6. (Discovery): Replacement candidate identified: https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng (Candidate title: 'Commission Delegated Regulation (EU) 2023/2772 (ESRS Set 1)', Verified: False)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>European Union</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>EN EN - o n a v o l u n t a r y s u s</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>http://ec.europa.eu/finance/docs/law/250730-recommendation-vsme_en.pdf</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>PDF_VALID</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
@@ -15890,6 +15882,57 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/eli/reg/2019/2088</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Document contains explicit amendment references or is an amending instrument.</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>Why was this marked MANUAL_REVIEW?
+1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex')
+5. (Identity): Regulatory identity: EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="12" t="n">
         <v>10</v>
@@ -15901,12 +15944,12 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/reg/2019/2088</t>
+          <t>https://eur-lex.europa.eu/eli/reg/2020/852</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -15916,28 +15959,28 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>AMENDED</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Document contains explicit amendment references or is an amending instrument.</t>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex')
-5. (Identity): Regulatory identity: EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
+5. (Identity): Regulatory identity: Search results - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -15952,12 +15995,12 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Search results - EUR-Lex</t>
+          <t>Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/reg/2020/852</t>
+          <t>https://eur-lex.europa.eu/eli/dir/2024/1760/oj/eng</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -15984,10 +16027,10 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
-5. (Identity): Regulatory identity: Search results - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex')
+5. (Identity): Regulatory identity: Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex (Consultation / Draft) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
@@ -16003,12 +16046,12 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/dir/2024/1760/oj/eng</t>
+          <t>https://eur-lex.europa.eu/eli/dir/2003/87</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -16018,28 +16061,28 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+          <t>Document contains explicit amendment references or is an amending instrument.</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex')
-5. (Identity): Regulatory identity: Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex (Consultation / Draft) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex')
+5. (Identity): Regulatory identity: EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -16054,42 +16097,43 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/dir/2003/87</t>
+          <t>https://eur-lex.europa.eu/eli/dir/2018/2001</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>Access Blocked / Bot Challenge Unresolved</t>
+          <t>Document contains explicit amendment references or is an amending instrument.</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Identity): Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex')
+5. (Identity): Regulatory identity: EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -16104,12 +16148,12 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/dir/2018/2001</t>
+          <t>https://eur-lex.europa.eu/eli/dir/2018/2002</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -16119,7 +16163,7 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>AMENDED</t>
+          <t>SUPERSEDED</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -16129,18 +16173,18 @@
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>Document contains explicit amendment references or is an amending instrument.</t>
+          <t>Document explicitly superseded/repealed</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex')
-5. (Identity): Regulatory identity: EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-6. (Currentness): Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
+5. (Identity): Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+6. (Currentness): Lifecycle: SUPERSEDED (Document explicitly superseded/repealed) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed)</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16204,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/dir/2018/2002</t>
+          <t>https://eur-lex.europa.eu/eli/dir/2009/125</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -16170,28 +16214,28 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>SUPERSEDED</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>Document explicitly superseded/repealed</t>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
 5. (Identity): Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-6. (Currentness): Lifecycle: SUPERSEDED (Document explicitly superseded/repealed) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed)</t>
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -16211,7 +16255,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/dir/2009/125</t>
+          <t>https://eur-lex.europa.eu/eli/reg/2023/1115</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -16238,10 +16282,10 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
-5. (Identity): Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')
+5. (Identity): Regulatory identity: Search results - EUR-Lex (Delegated Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
@@ -16252,22 +16296,22 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>European Union</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>JavaScript is disabled</t>
+          <t>Business responsibility and sustainability reporting by listed entities</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/reg/2023/1115</t>
+          <t>https://www.sebi.gov.in/legal/circulars/may-2021/business-responsibility-and-sustainability-reporting-by-listed-entities_50096.html</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -16277,65 +16321,15 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>Access Blocked / Bot Challenge Unresolved</t>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)
-4. (Identity): Regulatory identity: JavaScript is disabled (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Business responsibility and sustainability reporting by listed entities</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>https://www.sebi.gov.in/legal/circulars/may-2021/business-responsibility-and-sustainability-reporting-by-listed-entities_50096.html</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
-        </is>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')
@@ -16346,6 +16340,57 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>https://www.mca.gov.in/Ministry/pdf/CompaniesAct2013.pdf</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>Why was this marked MANUAL_REVIEW?
+1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')
+2. (Technical): HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Corporate Affairs (MCA)) (Domain www.mca.gov.in registered under India)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'HOME')
+5. (Identity): Regulatory identity: HOME (Act / Legislation) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Ministry of Corporate Affairs (MCA))
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Corporate Affairs (MCA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" s="12" t="n">
         <v>19</v>
@@ -16357,17 +16402,17 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Error page</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>https://www.mca.gov.in/Ministry/pdf/CompaniesAct2013.pdf</t>
+          <t>https://www.rbi.org.in/Scripts/NotificationUser.aspx?Id=12213&amp;Mode=0</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>ACCESSIBLE_VIA_BROWSER</t>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -16386,57 +16431,6 @@
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Corporate Affairs (MCA)) (Domain www.mca.gov.in registered under India)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Error page')
-5. (Identity): Regulatory identity: Error page (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Ministry of Corporate Affairs (MCA))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Corporate Affairs (MCA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>https://www.rbi.org.in/Scripts/NotificationUser.aspx?Id=12213&amp;Mode=0</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')
@@ -16447,46 +16441,46 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Kingdom of Saudi Arabia</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>ESG Disclosure Guidelines</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>https://sseinitiative.org/sites/sseinitiative/files/documents/tadawul-esg-disclosure-guidelines-en.pdf</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>PDF_VALID</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Kingdom of Saudi Arabia' (Exact match with target jurisdiction: 'Kingdom of Saudi Arabia')
@@ -16498,28 +16492,79 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>ESG Reporting Guide</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.boursakuwait.com.kw/en/resources/e-publications/esg-reporting-guide</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>Why was this marked MANUAL_REVIEW?
+1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Kuwait' (Exact match with target jurisdiction: 'Kuwait')
+2. (Technical): HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Boursa Kuwait) (Domain www.boursakuwait.com.kw registered under Kuwait)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'ESG Reporting Guide')
+5. (Identity): Regulatory identity: ESG Reporting Guide (Guideline / Standard) (Topic: Corporate Governance &amp; CSR, Population: Listed Companies / Issuers, Authority: Boursa Kuwait)
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Boursa Kuwait (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="12" t="n">
         <v>22</v>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>ESG Reporting Guide</t>
+          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>https://www.boursakuwait.com.kw/en/resources/e-publications/esg-reporting-guide</t>
+          <t>https://www.msx.om/MSMDOCS/downloads/ESG-MSX-E.pdf</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>ACCESSIBLE_VIA_BROWSER</t>
+          <t>PDF_VALID</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -16538,57 +16583,6 @@
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Kuwait' (Exact match with target jurisdiction: 'Kuwait')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Boursa Kuwait) (Domain www.boursakuwait.com.kw registered under Kuwait)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'ESG Reporting Guide')
-5. (Identity): Regulatory identity: ESG Reporting Guide (Guideline / Standard) (Topic: Corporate Governance &amp; CSR, Population: Listed Companies / Issuers, Authority: Boursa Kuwait)
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Boursa Kuwait (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>https://www.msx.om/MSMDOCS/downloads/ESG-MSX-E.pdf</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>PDF_VALID</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
-        </is>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Oman' (Exact match with target jurisdiction: 'Oman')
@@ -16600,46 +16594,46 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>ESG Initiative</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>https://www.qe.com.qa/esg-del</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>LIVE</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Qatar' (Exact match with target jurisdiction: 'Qatar')
@@ -16650,46 +16644,46 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>https://rulebook.sgx.com/rulebook/practice-note-76-sustainability-reporting-guide</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>LIVE</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')
@@ -16700,6 +16694,56 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.mas.gov.sg/-/media/MAS/News-and-Publications/Consultation-Papers/CP13-Guidelines-on-Environmental-Risk-Management/Guidelines_on_Environmental_Risk_Management.pdf</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>Why was this marked MANUAL_REVIEW?
+1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')
+2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
+4. (Identity): Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
+5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
       <c r="A28" s="12" t="n">
         <v>26</v>
@@ -16711,24 +16755,24 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>https://www.mas.gov.sg/regulation/guidelines/guidelines-on-environmental-risk-management-for-asset-managers</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>https://www.mas.gov.sg/-/media/MAS/News-and-Publications/Consultation-Papers/CP13-Guidelines-on-Environmental-Risk-Management/Guidelines_on_Environmental_Risk_Management.pdf</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>HTTP_404</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
           <t>55%</t>
@@ -16741,14 +16785,12 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>Why was this marked REPLACE?
+          <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')
-2. (Technical): Redirect detected (healthy_redirect) to: https://www.mas.gov.sg/Custom/errorpages/PageNotFound.aspx (Redirect chain length: 1)
-3. (Technical): HTTP 404 (HTTP_404) (Content-Type: text/html; charset=utf-8, Latency: 0ms)
-4. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
-5. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)
-7. (Discovery): Replacement candidate identified: https://www.mas.gov.sg/regulation/guidelines/guidelines-on-environmental-risk-management (Candidate title: 'Monetary Authority of Singapore (MAS) Guidelines on Environmental Risk Management', Verified: True)</t>
+2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
+4. (Identity): Regulatory identity: Maintenance (Regulation) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
+5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -16763,12 +16805,12 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Guidelines on Environmental Risk Management for Asset Managers</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>https://www.mas.gov.sg/regulation/guidelines/guidelines-on-environmental-risk-management-for-asset-managers</t>
+          <t>https://www.mas.gov.sg/news/media-releases/2022/singapore-green-bond-framework-introduced-for-upcoming-inaugural-singapore-sovereign-green-bond-issuance</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -16795,9 +16837,9 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')
-2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)
+2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
-4. (Identity): Regulatory identity: Guidelines on Environmental Risk Management for Asset Managers (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Financial Institutions / Asset Managers, Authority: Monetary Authority of Singapore (MAS))
+4. (Identity): Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
 5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
@@ -16808,22 +16850,22 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance</t>
+          <t>Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental,</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>https://www.mas.gov.sg/news/media-releases/2022/singapore-green-bond-framework-introduced-for-upcoming-inaugural-singapore-sovereign-green-bond-issuance</t>
+          <t>https://www.adx.ae/-/media/adx/related-documents/sustainability/esg-disclosure-guidance-for-listed-companies---english.pdf</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>LIVE</t>
+          <t>PDF_VALID</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -16842,56 +16884,6 @@
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')
-2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)
-4. (Identity): Regulatory identity: Singapore Green Bond Framework Introduced for Upcoming Inaugural Singapore Sovereign Green Bond Issuance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental,</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>https://www.adx.ae/-/media/adx/related-documents/sustainability/esg-disclosure-guidance-for-listed-companies---english.pdf</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>PDF_VALID</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
-        </is>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
@@ -16903,46 +16895,46 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>United Arab Emirates</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>https://adxservices.adx.ae/WebServices/DataServices/contentDownload.aspx?doc=1704806</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>LIVE</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
@@ -16954,46 +16946,46 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>United Arab Emirates</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>https://www.ecgi.global/sites/default/files/codes/documents/chairman_of_authoritys_board_of_directors_decision_no._3_chairman_of_2020_concerning_approval_of_joint_stock_companies_governance_guide_3.pdf</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>PDF_VALID</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H32" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
@@ -17006,46 +16998,46 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>United Arab Emirates</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>https://www.sca.gov.ae/services/AjaxHandler.asmx/LoadRegulationByIdAsPdf?id=198&amp;lang=en&amp;title=Chairman+of+Authority%E2%80%99s+Board+of+Directors%E2%80%99+Decision+no.+%283%2FChairman%29+of+2020+concerning+Approval+of+Joint+Stock+Companies+Governance+Guide</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>LIVE</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
@@ -17057,6 +17049,57 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>https://uaelegislation.gov.ae/en/legislations/2521/download</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>Why was this marked MANUAL_REVIEW?
+1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (UAE Official Legislation) (Domain uaelegislation.gov.ae registered under United Arab Emirates)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: '')
+5. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UAE Official Legislation)
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UAE Official Legislation (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" s="12" t="n">
         <v>33</v>
@@ -17068,42 +17111,44 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
+          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>https://rulebook.centralbank.ae/en/rulebook/principles-sustainability-related-disclosures</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>PDF_VALID</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>https://uaelegislation.gov.ae/en/legislations/2521/download</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>ACCESS_BLOCKED</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>Access Blocked / Bot Challenge Unresolved</t>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (UAE Official Legislation) (Domain uaelegislation.gov.ae registered under United Arab Emirates)
-4. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UAE Official Legislation)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UAE Official Legislation (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of the UAE (CBUAE)) (Domain rulebook.centralbank.ae registered under United Arab Emirates)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Principles for Sustainability-Related Disclosures | CBUAE Rulebook')
+5. (Browser): Discovered underlying PDF: https://www.centralbank.ae/media/ivfkvbak/cbuae-code-of-conduct-blue-en-r5-5-pdf_2021.pdf (Magic %PDF- bytes verified.)
+6. (Identity): Regulatory identity: Principles for Sustainability-Related Disclosures | CBUAE Rulebook (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Central Bank of the UAE (CBUAE))
+7. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of the UAE (CBUAE) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -17113,22 +17158,22 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
+          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>https://rulebook.centralbank.ae/en/rulebook/principles-sustainability-related-disclosures</t>
+          <t>https://assets.publishing.service.gov.uk/media/62138625d3bf7f4f05879a21/mandatory-climate-related-financial-disclosures-publicly-quoted-private-cos-llps.pdf</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>LIVE</t>
+          <t>PDF_VALID</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -17147,56 +17192,6 @@
         </is>
       </c>
       <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')
-2. (Technical): HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of the UAE (CBUAE)) (Domain rulebook.centralbank.ae registered under United Arab Emirates)
-4. (Identity): Regulatory identity: Principles for Sustainability-Related Disclosures | CBUAE Rulebook (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Central Bank of the UAE (CBUAE))
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of the UAE (CBUAE) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>https://assets.publishing.service.gov.uk/media/62138625d3bf7f4f05879a21/mandatory-climate-related-financial-disclosures-publicly-quoted-private-cos-llps.pdf</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>PDF_VALID</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
-        </is>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')
@@ -17208,6 +17203,57 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Environment Act 2021</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>https://www.legislation.gov.uk/ukpga/2021/30/contents/enacted</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>Why was this marked MANUAL_REVIEW?
+1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Environment Act 2021')
+5. (Identity): Regulatory identity: Environment Act 2021 (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
       <c r="A38" s="12" t="n">
         <v>36</v>
@@ -17219,12 +17265,12 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>Environment Act 2021</t>
+          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>https://www.legislation.gov.uk/ukpga/2021/30/contents/enacted</t>
+          <t>https://www.legislation.gov.uk/uksi/2022/31/contents/made</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -17251,10 +17297,10 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'Environment Act 2021')
-5. (Identity): Regulatory identity: Environment Act 2021 (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022')
+5. (Identity): Regulatory identity: The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022 (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))
 6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
@@ -17265,48 +17311,49 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>https://www.legislation.gov.uk/uksi/2022/31/contents/made</t>
+          <t>https://www.sec.gov/files/rules/final/2024/33-11275.pdf</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>ACCESSIBLE_VIA_BROWSER</t>
+          <t>PDF_VALID</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>CONSULTATION</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+          <t>Consultation / Draft paper without confirmed final regulation</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')
-2. (Technical): HTTP 202 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022')
-5. (Identity): Regulatory identity: The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022 (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')
+2. (Technical): HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission (SEC)) (Domain www.sec.gov registered under United States)
+4. (Document): PDF document verified with magic bytes %PDF- (Pages: 885, Text length: 5000)
+5. (Identity): Regulatory identity: Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission (SEC))
+6. (Currentness): Lifecycle: CONSULTATION (Document is a consultation paper or draft proposal, not a final binding regulation.) (Issuing authority verified as authoritative: Securities and Exchange Commission (SEC) (TIER_1_PRIMARY_REGULATOR); Document contains draft/consultation markers; not a final regulation.)
+7. (Discovery): Replacement candidate identified: https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors (Candidate title: 'SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)', Verified: False)</t>
         </is>
       </c>
     </row>
@@ -17321,43 +17368,43 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
+          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dol.gov/newsroom/releases/ebsa/ebsa20221122</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>ACCESSIBLE_VIA_BROWSER</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/files/rules/final/2024/33-11275.pdf</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>ACCESS_BLOCKED</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>Access Blocked / Bot Challenge Unresolved</t>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission (SEC)) (Domain www.sec.gov registered under United States)
-4. (Identity): Regulatory identity: UNKNOWN (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission (SEC))
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Commission (SEC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)
-6. (Discovery): Replacement candidate identified: https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors (Candidate title: 'SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)', Verified: False)</t>
+2. (Technical): HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Department of Labor (DOL / EBSA)) (Domain www.dol.gov registered under United States)
+4. (Browser): Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor')
+5. (Identity): Regulatory identity: US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Department of Labor (DOL / EBSA))
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Department of Labor (DOL / EBSA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -17372,17 +17419,17 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
+          <t>Bill Text</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>https://www.dol.gov/newsroom/releases/ebsa/ebsa20221122</t>
+          <t>https://leginfo.legislature.ca.gov/faces/billTextClient.xhtml?bill_id=202120220SB253</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>ACCESSIBLE_VIA_BROWSER</t>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -17401,57 +17448,6 @@
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Department of Labor (DOL / EBSA)) (Domain www.dol.gov registered under United States)
-4. (Browser): Browser bypassed bot challenge (HTTP 200 -&gt; 200) (Resolved page title: 'US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor')
-5. (Identity): Regulatory identity: US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Department of Labor (DOL / EBSA))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Department of Labor (DOL / EBSA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>Bill Text</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>https://leginfo.legislature.ca.gov/faces/billTextClient.xhtml?bill_id=202120220SB253</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
-        </is>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')
@@ -17462,46 +17458,46 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>https://nesrea.gov.ng/wp-content/uploads/2025/05/NESREA-ACT-1.pdf</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>PDF_VALID</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I43" s="13" t="inlineStr">
+      <c r="I42" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
@@ -17513,46 +17509,46 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>https://nesrea.gov.ng/wp-content/uploads/2025/05/NESREA_Ammended_Act_2018-1.pdf</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>PDF_VALID</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I44" s="13" t="inlineStr">
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
@@ -17564,46 +17560,46 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>https://www.policyvault.africa/policy/environmental-impact-assessment-act-2/</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>LIVE</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I45" s="13" t="inlineStr">
+      <c r="I44" s="13" t="inlineStr">
         <is>
           <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
@@ -17616,6 +17612,56 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>CONNECTION_ERROR</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>Why was this marked MANUAL_REVIEW?
+1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
+2. (Technical): HTTP None (CONNECTION_ERROR) (Content-Type: , Latency: 0ms)
+3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)
+4. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))
+5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
       <c r="A46" s="12" t="n">
         <v>44</v>
@@ -17627,17 +17673,17 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>www.cac.gov.ng</t>
+          <t>Policies &amp; Guidelines</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf</t>
+          <t>https://nesrea.gov.ng/policies-guidelines/</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_BLOCKED</t>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -17647,66 +17693,15 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>Access Blocked / Bot Challenge Unresolved</t>
+          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
-1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)
-4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
-5. (Identity): Regulatory identity: www.cac.gov.ng (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>Policies &amp; Guidelines</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>https://nesrea.gov.ng/policies-guidelines/</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
-        </is>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
@@ -17718,46 +17713,46 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>https://unfccc.int/sites/default/files/NDC/2022-06/NDC%20INTERIM%20REPORT%20SUBMISSION%20-%20NIGERIA.pdf</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>PDF_VALID</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I48" s="13" t="inlineStr">
+      <c r="I47" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
@@ -17770,50 +17765,50 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>www.cbn.gov.ng</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>https://www.cbn.gov.ng/out/2012/ccd/circular-nsbp.pdf</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>ACCESS_BLOCKED</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>BOT_PROTECTION</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>Access Blocked / Bot Challenge Unresolved</t>
         </is>
       </c>
-      <c r="I49" s="13" t="inlineStr">
+      <c r="I48" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
-2. (Technical): HTTP 403 (ACCESS_BLOCKED) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of Nigeria (CBN)) (Domain www.cbn.gov.ng registered under Nigeria)
 4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
 5. (Identity): Regulatory identity: www.cbn.gov.ng (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Central Bank of Nigeria (CBN))
@@ -17821,46 +17816,46 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>https://sec.gov.ng/documents/19/12-October-2018-SEC-NG-Approved-Rules.pdf</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>PDF_VALID</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="H49" s="13" t="inlineStr">
         <is>
           <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
         </is>
       </c>
-      <c r="I50" s="13" t="inlineStr">
+      <c r="I49" s="13" t="inlineStr">
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')

--- a/step_esg_pipeline/report.xlsx
+++ b/step_esg_pipeline/report.xlsx
@@ -590,7 +590,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Audit Timestamp: 2026-09-21 07:28 UTC | Scoped Links: 48 | Section: ESG Legislative Landscape</t>
+          <t>Audit Timestamp: 2026-09-21 08:04 UTC | Scoped Links: 48 | Section: ESG Legislative Landscape</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>https://www.sse.com.cn/disclosure/listedinfo/announcement/c/20240424_624053.html</t>
+          <t>https://static.sse.com.cn/disclosure/listedinfo/announcement/c/20240424_624053.html</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>TIMEOUT</t>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
@@ -1105,10 +1105,11 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')
-2. (Technical): HTTP None (TIMEOUT) (Content-Type: , Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Shanghai Stock Exchange) (Domain www.sse.com.cn registered under China)
-4. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Shanghai Stock Exchange)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Shanghai Stock Exchange (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+2. (Technical): Redirect detected (healthy_redirect) to: https://static.sse.com.cn/disclosure/listedinfo/announcement/c/20240424_624053.html (Redirect chain length: 1)
+3. (Technical): HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)
+4. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Shanghai Stock Exchange) (Domain static.sse.com.cn registered under China)
+5. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Shanghai Stock Exchange)
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Shanghai Stock Exchange (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1159,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>https://www.greenfinanceplatform.org/policies-and-regulations/chinas-administrative-measures-legal-disclosure-enterprise-environmental?__cf_chl_rt_tk=7288OQ.YtRNiXMXLWQZx1UTkIPnlBDkCHlljymeEwZE-1789975288-1.0.1.1-g.Ca2akZTj5DrhP1DOGBoaG4ofWiSID_KcHT2g1iGwI</t>
+          <t>https://www.greenfinanceplatform.org/policies-and-regulations/chinas-administrative-measures-legal-disclosure-enterprise-environmental?__cf_chl_rt_tk=17lt_lL2zfN8EOMGRpuh5BhOQ7LpXV_hz93ztrNH96c-1789977311-1.0.1.1-45cx3n79_aWCEAVHoWHR88o8PH0gS3EOOt77evahBno</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
@@ -6252,127 +6253,149 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>ESG Legislative Landscape</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>www.cac.gov.ng</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Guideline / Standard</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>Sustainability &amp; ESG Reporting</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Listed Companies / Issuers</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf?__cf_chl_rt_tk=JC52Kj70C.CuhJH_GXXSz_28.3PpR2MkIG3REnHaenE-1789977688-1.0.1.1-6acOe6CeyEPlFn0ZQJikHWPmBCUfsuWmCvKxHkX53do</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>BOT_PROTECTION</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>Just a moment...</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="inlineStr">
+        <is>
+          <t>Corporate Affairs Commission (CAC)</t>
+        </is>
+      </c>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>TIER_1_OFFICIAL_REGULATOR</t>
+        </is>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Guideline / Standard</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability &amp; ESG Reporting</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Listed Companies / Issuers</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>CONNECTION_ERROR</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>Corporate Affairs Commission (CAC)</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>TIER_1_OFFICIAL_REGULATOR</t>
-        </is>
-      </c>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>NO_REPLACEMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="4" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="V47" s="4" t="inlineStr">
+      <c r="P47" s="9" t="inlineStr">
+        <is>
+          <t>https://icrp.cac.gov.ng/cama</t>
+        </is>
+      </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>Corporate Affairs Commission (CAC) CAMA 2020 Portal</t>
+        </is>
+      </c>
+      <c r="R47" s="8" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="S47" s="8" t="inlineStr">
+        <is>
+          <t>REPLACEMENT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="U47" s="7" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="V47" s="7" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="W47" s="4" t="inlineStr">
+      <c r="W47" s="7" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="X47" s="4" t="inlineStr">
+      <c r="X47" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="Y47" s="4" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="Z47" s="4" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="AA47" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL_REVIEW</t>
-        </is>
-      </c>
-      <c r="AB47" s="5" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
+      <c r="Y47" s="7" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="Z47" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="AA47" s="7" t="inlineStr">
+        <is>
+          <t>REPLACE</t>
+        </is>
+      </c>
+      <c r="AB47" s="8" t="inlineStr">
+        <is>
+          <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
-2. (Technical): HTTP None (CONNECTION_ERROR) (Content-Type: , Latency: 0ms)
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)
-4. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
+5. (Identity): Regulatory identity: www.cac.gov.ng (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)
+7. (Discovery): Replacement candidate identified: https://icrp.cac.gov.ng/cama (Candidate title: 'Corporate Affairs Commission (CAC) CAMA 2020 Portal', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -6646,132 +6669,149 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>ESG Legislative Landscape</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>www.cbn.gov.ng</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>Circular</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Sustainability &amp; ESG Reporting</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>Listed Companies / Issuers</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>https://www.cbn.gov.ng/out/2012/ccd/circular-nsbp.pdf</t>
         </is>
       </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>https://www.cbn.gov.ng/out/2012/ccd/circular-nsbp.pdf?__cf_chl_rt_tk=SafPVnuA4C0xdj9Om2UewRZNlCHcZP3L3SHDN0tz3K8-1789975702-1.0.1.1-.FisoWRs0Ofi.MLW2JFwkwWsRQuubw.6jhiup6vHNqg</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cbn.gov.ng/out/2012/ccd/circular-nsbp.pdf?__cf_chl_rt_tk=cZl8BtbGvm0CghA2W1Q54e_a5G9XMtCzyoxX4R0FEvE-1789977852-1.0.1.1-9HO0r_a_VyQaVYEOUz_CJJerMTniQF4cl7o7aecuohA</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>BOT_PROTECTION</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="L50" s="8" t="inlineStr">
         <is>
           <t>Just a moment...</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="M50" s="8" t="inlineStr">
         <is>
           <t>Central Bank of Nigeria (CBN)</t>
         </is>
       </c>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="N50" s="8" t="inlineStr">
         <is>
           <t>TIER_1_OFFICIAL_REGULATOR</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O50" s="8" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr">
-        <is>
-          <t>NONE_FOUND</t>
-        </is>
-      </c>
-      <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="4" t="inlineStr">
+      <c r="P50" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cbn.gov.ng/documents/circulars.html</t>
+        </is>
+      </c>
+      <c r="Q50" s="8" t="inlineStr">
+        <is>
+          <t>Central Bank of Nigeria (CBN) Circulars (FPR/DIR/CIR/GEN/01/33 - NSBP)</t>
+        </is>
+      </c>
+      <c r="R50" s="8" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="S50" s="8" t="inlineStr">
+        <is>
+          <t>REPLACEMENT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="U50" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="V50" s="4" t="inlineStr">
+      <c r="V50" s="7" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="W50" s="4" t="inlineStr">
+      <c r="W50" s="7" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="X50" s="4" t="inlineStr">
+      <c r="X50" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="Y50" s="4" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="Z50" s="4" t="inlineStr">
+      <c r="Y50" s="7" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="Z50" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="AA50" s="4" t="inlineStr">
-        <is>
-          <t>MANUAL_REVIEW</t>
-        </is>
-      </c>
-      <c r="AB50" s="5" t="inlineStr">
-        <is>
-          <t>Why was this marked MANUAL_REVIEW?
+      <c r="AA50" s="7" t="inlineStr">
+        <is>
+          <t>REPLACE</t>
+        </is>
+      </c>
+      <c r="AB50" s="8" t="inlineStr">
+        <is>
+          <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
 2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of Nigeria (CBN)) (Domain www.cbn.gov.ng registered under Nigeria)
 4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
 5. (Identity): Regulatory identity: www.cbn.gov.ng (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Central Bank of Nigeria (CBN))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of Nigeria (CBN) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of Nigeria (CBN) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)
+7. (Discovery): Replacement candidate identified: https://www.cbn.gov.ng/documents/circulars.html (Candidate title: 'Central Bank of Nigeria (CBN) Circulars (FPR/DIR/CIR/GEN/01/33 - NSBP)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -7002,15 +7042,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7022,7 +7064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E287"/>
+  <dimension ref="A1:E291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7387,7 +7429,7 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>HTTP None (TIMEOUT) (Content-Type: , Latency: 0ms)</t>
+          <t>Redirect detected (healthy_redirect) to: https://static.sse.com.cn/disclosure/listedinfo/announcement/c/20240424_624053.html (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
@@ -7407,12 +7449,12 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Shanghai Stock Exchange) (Domain www.sse.com.cn registered under China)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -7432,12 +7474,12 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Shanghai Stock Exchange)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Shanghai Stock Exchange) (Domain static.sse.com.cn registered under China)</t>
         </is>
       </c>
     </row>
@@ -7457,18 +7499,18 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Shanghai Stock Exchange (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Shanghai Stock Exchange)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -7477,17 +7519,17 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>www.greenfinanceplatform.org</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Shanghai Stock Exchange (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -7507,12 +7549,12 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')</t>
         </is>
       </c>
     </row>
@@ -7532,12 +7574,12 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.greenfinanceplatform.org) (Domain www.greenfinanceplatform.org registered under China)</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7599,12 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.greenfinanceplatform.org) (Domain www.greenfinanceplatform.org registered under China)</t>
         </is>
       </c>
     </row>
@@ -7582,12 +7624,12 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: www.greenfinanceplatform.org (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)</t>
         </is>
       </c>
     </row>
@@ -7607,12 +7649,12 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: www.greenfinanceplatform.org (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
@@ -7632,18 +7674,18 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://www.mee.gov.cn/xxgk2018/xxgk/xxgk02/202112/t20211221_964720.html (Candidate title: 'Decree No. 24 of the Ministry of Ecology and Environment (China)', Verified: True)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
@@ -7652,17 +7694,17 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>您访问的链接即将离开生态环境部门户网站，是否继续？</t>
+          <t>www.greenfinanceplatform.org</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')</t>
+          <t>Replacement candidate identified: https://www.mee.gov.cn/xxgk2018/xxgk/xxgk02/202112/t20211221_964720.html (Candidate title: 'Decree No. 24 of the Ministry of Ecology and Environment (China)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7724,12 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://www.mee.gov.cn/404/index.shtml (Redirect chain length: 2)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7754,7 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Redirect detected (healthy_redirect) to: https://www.mee.gov.cn/404/index.shtml (Redirect chain length: 2)</t>
         </is>
       </c>
     </row>
@@ -7732,12 +7774,12 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Ecology and Environment) (Domain www.mee.gov.cn registered under China)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -7757,12 +7799,12 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: 您访问的链接即将离开生态环境部门户网站，是否继续？ (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Ministry of Ecology and Environment)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Ecology and Environment) (Domain www.mee.gov.cn registered under China)</t>
         </is>
       </c>
     </row>
@@ -7782,18 +7824,18 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Ecology and Environment (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: 您访问的链接即将离开生态环境部门户网站，是否继续？ (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Ministry of Ecology and Environment)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
@@ -7802,17 +7844,17 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>China’s emissions trading system (ETS) reforms: On track, but needs robust enforcement</t>
+          <t>您访问的链接即将离开生态环境部门户网站，是否继续？</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Ecology and Environment (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7874,12 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')</t>
         </is>
       </c>
     </row>
@@ -7857,12 +7899,12 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (ieefa.org) (Domain ieefa.org registered under China)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -7882,12 +7924,12 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: China’s emissions trading system (ETS) reforms: On track, but needs robust enforcement (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (ieefa.org) (Domain ieefa.org registered under China)</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7949,12 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: China’s emissions trading system (ETS) reforms: On track, but needs robust enforcement (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
@@ -7932,37 +7974,37 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://www.mee.gov.cn/ywgz/ydqhbh/qhgjyhxyyqyzcjgz/ (Candidate title: 'MEE Official ETS Portal (China)', Verified: True)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>European Union</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex</t>
+          <t>China’s emissions trading system (ETS) reforms: On track, but needs robust enforcement</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Replacement candidate identified: https://www.mee.gov.cn/ywgz/ydqhbh/qhgjyhxyyqyzcjgz/ (Candidate title: 'MEE Official ETS Portal (China)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -7982,12 +8024,12 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8049,12 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8074,12 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8057,12 +8099,12 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8082,18 +8124,18 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: SUPERSEDED (Document explicitly superseded/repealed by the following: ‘(5) “net turnover” means the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed by the following: ‘(5) “net turnover” means the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover)</t>
+          <t>Regulatory identity: EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
@@ -8102,17 +8144,17 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
+          <t>EUR-Lex - 02022L2464-20250417 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: SUPERSEDED (Document explicitly superseded/repealed by the following: ‘(5) “net turnover” means the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed by the following: ‘(5) “net turnover” means the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover)</t>
         </is>
       </c>
     </row>
@@ -8132,12 +8174,12 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8157,12 +8199,12 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8182,12 +8224,12 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Delegated regulation - EU - 2023/2772 - EN - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8207,12 +8249,12 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Delegated regulation - EU - 2023/2772 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Large Enterprises / PIEs, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Delegated regulation - EU - 2023/2772 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8274,12 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+          <t>Regulatory identity: Delegated regulation - EU - 2023/2772 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Large Enterprises / PIEs, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
@@ -8257,18 +8299,18 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng (Candidate title: 'Commission Delegated Regulation (EU) 2023/2772 (ESRS Set 1)', Verified: True)</t>
+          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
@@ -8277,17 +8319,17 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>EN EN - o n a v o l u n t a r y s u s</t>
+          <t>Delegated regulation - EU - 2023/2772 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Replacement candidate identified: https://eur-lex.europa.eu/eli/reg_del/2023/2772/oj/eng (Candidate title: 'Commission Delegated Regulation (EU) 2023/2772 (ESRS Set 1)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -8307,12 +8349,12 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://ec.europa.eu/finance/docs/law/250730-recommendation-vsme_en.pdf (Redirect chain length: 1)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8379,7 @@
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Redirect detected (healthy_redirect) to: https://ec.europa.eu/finance/docs/law/250730-recommendation-vsme_en.pdf (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
@@ -8357,12 +8399,12 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (European Commission) (Domain ec.europa.eu registered under European Union)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8424,12 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 8, Text length: 5000)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (European Commission) (Domain ec.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8449,12 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: EN EN - o n a v o l u n t a r y s u s (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: European Commission)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 8, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -8432,18 +8474,18 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: European Commission (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: EN EN - o n a v o l u n t a r y s u s (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: European Commission)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
@@ -8452,17 +8494,17 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex</t>
+          <t>EN EN - o n a v o l u n t a r y s u s</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: European Commission (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -8482,12 +8524,12 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8507,12 +8549,12 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8532,12 +8574,12 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8599,12 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8582,18 +8624,18 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+          <t>Regulatory identity: EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
@@ -8602,17 +8644,17 @@
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>Search results - EUR-Lex</t>
+          <t>EUR-Lex - 02019R2088-20260702 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -8632,12 +8674,12 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8657,12 +8699,12 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8682,12 +8724,12 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8749,12 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Search results - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8732,18 +8774,18 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Search results - EUR-Lex (Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
@@ -8752,17 +8794,17 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -8782,12 +8824,12 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8849,12 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8832,12 +8874,12 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8899,12 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex (Consultation / Draft) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -8882,18 +8924,18 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex (Consultation / Draft) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
@@ -8902,17 +8944,17 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
+          <t>Directive - EU - 2024/1760 - EN - CSDDD - EUR-Lex</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8974,12 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -8957,12 +8999,12 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -8982,12 +9024,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -9007,12 +9049,12 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -9032,18 +9074,18 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+          <t>Regulatory identity: EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex (Directive) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
@@ -9052,17 +9094,17 @@
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex</t>
+          <t>EUR-Lex - 02003L0087-20240301 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -9082,12 +9124,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -9107,12 +9149,12 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9132,12 +9174,12 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -9157,12 +9199,12 @@
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -9182,18 +9224,18 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
+          <t>Regulatory identity: EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
@@ -9202,17 +9244,17 @@
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>Search results - EUR-Lex</t>
+          <t>EUR-Lex - 02018L2001-20240716 - EN - EUR-Lex</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: AMENDED (Document contains explicit amendment references or is an amending instrument.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document contains explicit amendment references or is an amending instrument.)</t>
         </is>
       </c>
     </row>
@@ -9232,12 +9274,12 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9299,12 @@
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9282,12 +9324,12 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -9307,12 +9349,12 @@
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -9332,18 +9374,18 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: SUPERSEDED (Document explicitly superseded/repealed) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed)</t>
+          <t>Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
@@ -9357,12 +9399,12 @@
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: SUPERSEDED (Document explicitly superseded/repealed) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Document explicitly superseded/repealed)</t>
         </is>
       </c>
     </row>
@@ -9382,12 +9424,12 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9449,12 @@
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9432,12 +9474,12 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -9457,12 +9499,12 @@
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -9482,18 +9524,18 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Search results - EUR-Lex (Directive) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
@@ -9507,12 +9549,12 @@
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -9532,12 +9574,12 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'European Union' (Exact match with target jurisdiction: 'European Union')</t>
         </is>
       </c>
     </row>
@@ -9557,12 +9599,12 @@
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9582,12 +9624,12 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Official Journal of the European Union) (Domain eur-lex.europa.eu registered under European Union)</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9649,12 @@
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Search results - EUR-Lex (Delegated Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Search results - EUR-Lex')</t>
         </is>
       </c>
     </row>
@@ -9632,37 +9674,37 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Search results - EUR-Lex (Delegated Regulation) (Topic: Due Diligence &amp; Supply Chain, Population: Listed Companies / Issuers, Authority: Official Journal of the European Union)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>European Union</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>Business responsibility and sustainability reporting by listed entities</t>
+          <t>Search results - EUR-Lex</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Official Journal of the European Union (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -9682,12 +9724,12 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
         </is>
       </c>
     </row>
@@ -9707,12 +9749,12 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Board of India (SEBI)) (Domain www.sebi.gov.in registered under India)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9732,12 +9774,12 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Business responsibility and sustainability reporting by listed entities (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Securities and Exchange Board of India (SEBI))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Board of India (SEBI)) (Domain www.sebi.gov.in registered under India)</t>
         </is>
       </c>
     </row>
@@ -9757,18 +9799,18 @@
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Board of India (SEBI) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Business responsibility and sustainability reporting by listed entities (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Securities and Exchange Board of India (SEBI))</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
@@ -9777,17 +9819,17 @@
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>Business responsibility and sustainability reporting by listed entities</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Board of India (SEBI) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -9807,12 +9849,12 @@
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9874,12 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Corporate Affairs (MCA)) (Domain www.mca.gov.in registered under India)</t>
+          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9899,12 @@
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'HOME')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Ministry of Corporate Affairs (MCA)) (Domain www.mca.gov.in registered under India)</t>
         </is>
       </c>
     </row>
@@ -9882,12 +9924,12 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: HOME (Act / Legislation) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Ministry of Corporate Affairs (MCA))</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'HOME')</t>
         </is>
       </c>
     </row>
@@ -9907,18 +9949,18 @@
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Corporate Affairs (MCA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: HOME (Act / Legislation) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Ministry of Corporate Affairs (MCA))</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
@@ -9927,17 +9969,17 @@
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Ministry of Corporate Affairs (MCA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -9957,12 +9999,12 @@
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'India' (Exact match with target jurisdiction: 'India')</t>
         </is>
       </c>
     </row>
@@ -9982,12 +10024,12 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Reserve Bank of India (RBI)) (Domain www.rbi.org.in registered under India)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10007,12 +10049,12 @@
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Notifications (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Reserve Bank of India (RBI))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Reserve Bank of India (RBI)) (Domain www.rbi.org.in registered under India)</t>
         </is>
       </c>
     </row>
@@ -10032,37 +10074,37 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Reserve Bank of India (RBI) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Notifications (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Reserve Bank of India (RBI))</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>Kingdom of Saudi Arabia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>ESG Disclosure Guidelines</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Kingdom of Saudi Arabia' (Exact match with target jurisdiction: 'Kingdom of Saudi Arabia')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Reserve Bank of India (RBI) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10082,12 +10124,12 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Kingdom of Saudi Arabia' (Exact match with target jurisdiction: 'Kingdom of Saudi Arabia')</t>
         </is>
       </c>
     </row>
@@ -10107,12 +10149,12 @@
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (sseinitiative.org) (Domain sseinitiative.org registered under Kingdom of Saudi Arabia)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10132,12 +10174,12 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 30, Text length: 5000)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (sseinitiative.org) (Domain sseinitiative.org registered under Kingdom of Saudi Arabia)</t>
         </is>
       </c>
     </row>
@@ -10157,12 +10199,12 @@
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: ESG Disclosure Guidelines (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 30, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -10182,37 +10224,37 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: ESG Disclosure Guidelines (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kingdom of Saudi Arabia</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>ESG Reporting Guide</t>
+          <t>ESG Disclosure Guidelines</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Kuwait' (Exact match with target jurisdiction: 'Kuwait')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10232,12 +10274,12 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Kuwait' (Exact match with target jurisdiction: 'Kuwait')</t>
         </is>
       </c>
     </row>
@@ -10257,12 +10299,12 @@
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Boursa Kuwait) (Domain www.boursakuwait.com.kw registered under Kuwait)</t>
+          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10282,12 +10324,12 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'ESG Reporting Guide')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Boursa Kuwait) (Domain www.boursakuwait.com.kw registered under Kuwait)</t>
         </is>
       </c>
     </row>
@@ -10307,12 +10349,12 @@
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: ESG Reporting Guide (Guideline / Standard) (Topic: Corporate Governance &amp; CSR, Population: Listed Companies / Issuers, Authority: Boursa Kuwait)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'ESG Reporting Guide')</t>
         </is>
       </c>
     </row>
@@ -10332,37 +10374,37 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Boursa Kuwait (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: ESG Reporting Guide (Guideline / Standard) (Topic: Corporate Governance &amp; CSR, Population: Listed Companies / Issuers, Authority: Boursa Kuwait)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
+          <t>ESG Reporting Guide</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Oman' (Exact match with target jurisdiction: 'Oman')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Boursa Kuwait (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10382,12 +10424,12 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Oman' (Exact match with target jurisdiction: 'Oman')</t>
         </is>
       </c>
     </row>
@@ -10407,12 +10449,12 @@
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Muscat Stock Exchange (MSX)) (Domain www.msx.om registered under Oman)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10432,12 +10474,12 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 18, Text length: 5000)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Muscat Stock Exchange (MSX)) (Domain www.msx.om registered under Oman)</t>
         </is>
       </c>
     </row>
@@ -10457,12 +10499,12 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: His Majesty Sultan Haitham bin Tariq - -God bless him- (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: All Commercial Enterprises, Authority: Muscat Stock Exchange (MSX))</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 18, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -10482,37 +10524,37 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Muscat Stock Exchange (MSX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: His Majesty Sultan Haitham bin Tariq - -God bless him- (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: All Commercial Enterprises, Authority: Muscat Stock Exchange (MSX))</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>ESG Initiative</t>
+          <t>His Majesty Sultan Haitham bin Tariq - -God bless him-</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Qatar' (Exact match with target jurisdiction: 'Qatar')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Muscat Stock Exchange (MSX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10532,12 +10574,12 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html;charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Qatar' (Exact match with target jurisdiction: 'Qatar')</t>
         </is>
       </c>
     </row>
@@ -10557,12 +10599,12 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Qatar Stock Exchange (QSE)) (Domain www.qe.com.qa registered under Qatar)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html;charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10582,12 +10624,12 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: ESG Initiative (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Qatar Stock Exchange (QSE))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Qatar Stock Exchange (QSE)) (Domain www.qe.com.qa registered under Qatar)</t>
         </is>
       </c>
     </row>
@@ -10607,37 +10649,37 @@
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Qatar Stock Exchange (QSE) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: ESG Initiative (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Qatar Stock Exchange (QSE))</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
+          <t>ESG Initiative</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Qatar Stock Exchange (QSE) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10657,12 +10699,12 @@
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
         </is>
       </c>
     </row>
@@ -10682,12 +10724,12 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Singapore Exchange (SGX Group)) (Domain rulebook.sgx.com registered under Singapore)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10707,12 +10749,12 @@
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Practice Note 7.6 Sustainability Reporting Guide | Rulebooks (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Singapore Exchange (SGX Group))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Singapore Exchange (SGX Group)) (Domain rulebook.sgx.com registered under Singapore)</t>
         </is>
       </c>
     </row>
@@ -10732,18 +10774,18 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Singapore Exchange (SGX Group) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Practice Note 7.6 Sustainability Reporting Guide | Rulebooks (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Singapore Exchange (SGX Group))</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
@@ -10752,17 +10794,17 @@
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Practice Note 7.6 Sustainability Reporting Guide | Rulebooks</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Singapore Exchange (SGX Group) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10782,12 +10824,12 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
         </is>
       </c>
     </row>
@@ -10807,12 +10849,12 @@
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10832,12 +10874,12 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
         </is>
       </c>
     </row>
@@ -10857,18 +10899,18 @@
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
@@ -10882,12 +10924,12 @@
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -10907,12 +10949,12 @@
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
         </is>
       </c>
     </row>
@@ -10932,12 +10974,12 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -10957,12 +10999,12 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Maintenance (Regulation) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
         </is>
       </c>
     </row>
@@ -10982,18 +11024,18 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Maintenance (Regulation) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
@@ -11007,12 +11049,12 @@
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11032,12 +11074,12 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Singapore' (Exact match with target jurisdiction: 'Singapore')</t>
         </is>
       </c>
     </row>
@@ -11057,12 +11099,12 @@
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11124,12 @@
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Monetary Authority of Singapore (MAS)) (Domain www.mas.gov.sg registered under Singapore)</t>
         </is>
       </c>
     </row>
@@ -11107,37 +11149,37 @@
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Maintenance (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Monetary Authority of Singapore (MAS))</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
         <is>
-          <t>Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental,</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Monetary Authority of Singapore (MAS) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11157,12 +11199,12 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11182,12 +11224,12 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Abu Dhabi Securities Exchange (ADX)) (Domain www.adx.ae registered under United Arab Emirates)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11207,12 +11249,12 @@
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 40, Text length: 5000)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Abu Dhabi Securities Exchange (ADX)) (Domain www.adx.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11232,12 +11274,12 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental, (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Abu Dhabi Securities Exchange (ADX))</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 40, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -11257,18 +11299,18 @@
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Abu Dhabi Securities Exchange (ADX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental, (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Abu Dhabi Securities Exchange (ADX))</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
@@ -11277,17 +11319,17 @@
       </c>
       <c r="C171" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Environmental, Social and Governance (ESG) Disclosure Guidance for Listed Companies - Environmental,</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Abu Dhabi Securities Exchange (ADX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11307,12 +11349,12 @@
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://adxservices.adx.ae/webservices/dataservices/error.html?aspxerrorpath=/WebServices/DataServices/contentDownload.aspx (Redirect chain length: 1)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11337,7 +11379,7 @@
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Redirect detected (healthy_redirect) to: https://adxservices.adx.ae/webservices/dataservices/error.html?aspxerrorpath=/WebServices/DataServices/contentDownload.aspx (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
@@ -11357,12 +11399,12 @@
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Abu Dhabi Securities Exchange (ADX)) (Domain adxservices.adx.ae registered under United Arab Emirates)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11382,12 +11424,12 @@
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Abu Dhabi Securities Exchange (ADX))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Abu Dhabi Securities Exchange (ADX)) (Domain adxservices.adx.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11407,18 +11449,18 @@
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Abu Dhabi Securities Exchange (ADX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Abu Dhabi Securities Exchange (ADX))</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
@@ -11432,12 +11474,12 @@
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Abu Dhabi Securities Exchange (ADX) (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11457,12 +11499,12 @@
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11482,12 +11524,12 @@
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.ecgi.global) (Domain www.ecgi.global registered under United Arab Emirates)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11507,12 +11549,12 @@
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 0, Text length: 0)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.ecgi.global) (Domain www.ecgi.global registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11574,12 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 0, Text length: 0)</t>
         </is>
       </c>
     </row>
@@ -11557,12 +11599,12 @@
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
@@ -11582,18 +11624,18 @@
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://www.sca.gov.ae/en/regulations/regulations-listing.aspx (Candidate title: 'SCA Regulations Listing Portal (UAE)', Verified: True)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
@@ -11602,17 +11644,17 @@
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Replacement candidate identified: https://www.sca.gov.ae/en/regulations/regulations-listing.aspx (Candidate title: 'SCA Regulations Listing Portal (UAE)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -11632,12 +11674,12 @@
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (moderate_redirect) to: https://www.uaecma.gov.ae/en/home (Redirect chain length: 4)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11704,7 @@
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
+          <t>Redirect detected (moderate_redirect) to: https://www.uaecma.gov.ae/en/home (Redirect chain length: 4)</t>
         </is>
       </c>
     </row>
@@ -11682,12 +11724,12 @@
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (www.uaecma.gov.ae) (Domain www.uaecma.gov.ae registered under United Arab Emirates)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11707,12 +11749,12 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Services (Consultation / Draft) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (www.uaecma.gov.ae) (Domain www.uaecma.gov.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11732,18 +11774,18 @@
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Services (Consultation / Draft) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
@@ -11752,17 +11794,17 @@
       </c>
       <c r="C190" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11824,12 @@
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11807,12 +11849,12 @@
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UAE Official Legislation) (Domain uaelegislation.gov.ae registered under United Arab Emirates)</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11832,12 +11874,12 @@
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: '')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UAE Official Legislation) (Domain uaelegislation.gov.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -11857,12 +11899,12 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UAE Official Legislation)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: '')</t>
         </is>
       </c>
     </row>
@@ -11882,18 +11924,18 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UAE Official Legislation (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: UAE Official Legislation)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
@@ -11902,17 +11944,17 @@
       </c>
       <c r="C196" s="13" t="inlineStr">
         <is>
-          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UAE Official Legislation (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -11932,12 +11974,12 @@
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Arab Emirates' (Exact match with target jurisdiction: 'United Arab Emirates')</t>
         </is>
       </c>
     </row>
@@ -11957,12 +11999,12 @@
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of the UAE (CBUAE)) (Domain rulebook.centralbank.ae registered under United Arab Emirates)</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -11982,12 +12024,12 @@
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Principles for Sustainability-Related Disclosures | CBUAE Rulebook')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of the UAE (CBUAE)) (Domain rulebook.centralbank.ae registered under United Arab Emirates)</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12054,7 @@
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Discovered underlying PDF: https://www.centralbank.ae/media/ivfkvbak/cbuae-code-of-conduct-blue-en-r5-5-pdf_2021.pdf (Magic %PDF- bytes verified.)</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Principles for Sustainability-Related Disclosures | CBUAE Rulebook')</t>
         </is>
       </c>
     </row>
@@ -12032,12 +12074,12 @@
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Principles for Sustainability-Related Disclosures | CBUAE Rulebook (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Central Bank of the UAE (CBUAE))</t>
+          <t>Discovered underlying PDF: https://www.centralbank.ae/media/ivfkvbak/cbuae-code-of-conduct-blue-en-r5-5-pdf_2021.pdf (Magic %PDF- bytes verified.)</t>
         </is>
       </c>
     </row>
@@ -12057,37 +12099,37 @@
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of the UAE (CBUAE) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Principles for Sustainability-Related Disclosures | CBUAE Rulebook (Guideline / Standard) (Topic: Sustainable Finance &amp; Green Bonds, Population: Listed Companies / Issuers, Authority: Central Bank of the UAE (CBUAE))</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C203" s="13" t="inlineStr">
         <is>
-          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
+          <t>Principles for Sustainability-Related Disclosures | CBUAE Rulebook</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of the UAE (CBUAE) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12107,12 +12149,12 @@
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
         </is>
       </c>
     </row>
@@ -12132,12 +12174,12 @@
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Government (BEIS / DESNZ / Cabinet Office)) (Domain assets.publishing.service.gov.uk registered under United Kingdom)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -12157,12 +12199,12 @@
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 23, Text length: 5000)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Government (BEIS / DESNZ / Cabinet Office)) (Domain assets.publishing.service.gov.uk registered under United Kingdom)</t>
         </is>
       </c>
     </row>
@@ -12182,12 +12224,12 @@
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Government (BEIS / DESNZ / Cabinet Office))</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 23, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -12207,18 +12249,18 @@
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Government (BEIS / DESNZ / Cabinet Office) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Government (BEIS / DESNZ / Cabinet Office))</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B209" s="13" t="inlineStr">
         <is>
@@ -12227,17 +12269,17 @@
       </c>
       <c r="C209" s="13" t="inlineStr">
         <is>
-          <t>Environment Act 2021</t>
+          <t>Mandatory climate-related financial disclosures by publicly quoted companies, large private companies and LLPs</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Government (BEIS / DESNZ / Cabinet Office) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12257,12 +12299,12 @@
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
         </is>
       </c>
     </row>
@@ -12282,12 +12324,12 @@
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -12307,12 +12349,12 @@
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Environment Act 2021')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12374,12 @@
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Environment Act 2021 (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'Environment Act 2021')</t>
         </is>
       </c>
     </row>
@@ -12357,18 +12399,18 @@
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Environment Act 2021 (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B215" s="13" t="inlineStr">
         <is>
@@ -12377,17 +12419,17 @@
       </c>
       <c r="C215" s="13" t="inlineStr">
         <is>
-          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
+          <t>Environment Act 2021</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12407,12 +12449,12 @@
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United Kingdom' (Exact match with target jurisdiction: 'United Kingdom')</t>
         </is>
       </c>
     </row>
@@ -12432,12 +12474,12 @@
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E217" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)</t>
+          <t>HTTP 202 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -12457,12 +12499,12 @@
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (UK Legislation (The National Archives)) (Domain www.legislation.gov.uk registered under United Kingdom)</t>
         </is>
       </c>
     </row>
@@ -12482,12 +12524,12 @@
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E219" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022 (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022')</t>
         </is>
       </c>
     </row>
@@ -12507,37 +12549,37 @@
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022 (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: UK Legislation (The National Archives))</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B221" s="13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C221" s="13" t="inlineStr">
         <is>
-          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
+          <t>The Companies (Strategic Report) (Climate-related Financial Disclosure) Regulations 2022</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E221" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: UK Legislation (The National Archives) (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12557,12 +12599,12 @@
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
         </is>
       </c>
     </row>
@@ -12582,12 +12624,12 @@
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E223" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission (SEC)) (Domain www.sec.gov registered under United States)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -12607,12 +12649,12 @@
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 885, Text length: 5000)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission (SEC)) (Domain www.sec.gov registered under United States)</t>
         </is>
       </c>
     </row>
@@ -12632,12 +12674,12 @@
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E225" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission (SEC))</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 885, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -12657,12 +12699,12 @@
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: CONSULTATION (Document is a consultation paper or draft proposal, not a final binding regulation.) (Issuing authority verified as authoritative: Securities and Exchange Commission (SEC) (TIER_1_PRIMARY_REGULATOR); Document contains draft/consultation markers; not a final regulation.)</t>
+          <t>Regulatory identity: Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors (Regulation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission (SEC))</t>
         </is>
       </c>
     </row>
@@ -12682,18 +12724,18 @@
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E227" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors (Candidate title: 'SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)', Verified: False)</t>
+          <t>Lifecycle: CONSULTATION (Document is a consultation paper or draft proposal, not a final binding regulation.) (Issuing authority verified as authoritative: Securities and Exchange Commission (SEC) (TIER_1_PRIMARY_REGULATOR); Document contains draft/consultation markers; not a final regulation.)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
@@ -12702,17 +12744,17 @@
       </c>
       <c r="C228" s="13" t="inlineStr">
         <is>
-          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
+          <t>Final rule: The Enhancement and Standardization of Climate-Related Disclosures for Investors</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
+          <t>Replacement candidate identified: https://www.sec.gov/rules-regulations/2024/03/enhancement-and-standardization-climate-related-disclosures-investors (Candidate title: 'SEC Climate-Related Disclosures Docket &amp; Litigation Stay Order (Release No. 33-11280)', Verified: False)</t>
         </is>
       </c>
     </row>
@@ -12732,12 +12774,12 @@
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E229" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
         </is>
       </c>
     </row>
@@ -12757,12 +12799,12 @@
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Department of Labor (DOL / EBSA)) (Domain www.dol.gov registered under United States)</t>
+          <t>HTTP 403 (ACCESS_RESTRICTED) (Content-Type: text/html, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12824,12 @@
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Department of Labor (DOL / EBSA)) (Domain www.dol.gov registered under United States)</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12849,12 @@
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Department of Labor (DOL / EBSA))</t>
+          <t>Browser accessed successfully (HTTP 200 -&gt; 200) (Resolved page title: 'US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor')</t>
         </is>
       </c>
     </row>
@@ -12832,18 +12874,18 @@
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Department of Labor (DOL / EBSA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Department of Labor (DOL / EBSA))</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
@@ -12852,17 +12894,17 @@
       </c>
       <c r="C234" s="13" t="inlineStr">
         <is>
-          <t>Bill Text</t>
+          <t>US Department of Labor announces final rule to remove barriers to considering environmental, social, governance factors in plan investments | U.S. Department of Labor</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Department of Labor (DOL / EBSA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12924,12 @@
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'United States' (Exact match with target jurisdiction: 'United States')</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12949,12 @@
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (California State Legislature) (Domain leginfo.legislature.ca.gov registered under United States)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -12932,12 +12974,12 @@
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Bill Text (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: California State Legislature)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (California State Legislature) (Domain leginfo.legislature.ca.gov registered under United States)</t>
         </is>
       </c>
     </row>
@@ -12957,37 +12999,37 @@
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: California State Legislature (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Bill Text (Act / Legislation) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: California State Legislature)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B239" s="13" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C239" s="13" t="inlineStr">
         <is>
-          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
+          <t>Bill Text</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: California State Legislature (TIER_1_OFFICIAL_LEGISLATION); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -13007,12 +13049,12 @@
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13032,12 +13074,12 @@
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -13057,12 +13099,12 @@
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 22, Text length: 5000)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
@@ -13082,12 +13124,12 @@
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 22, Text length: 5000)</t>
         </is>
       </c>
     </row>
@@ -13107,18 +13149,18 @@
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B245" s="13" t="inlineStr">
         <is>
@@ -13127,17 +13169,17 @@
       </c>
       <c r="C245" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>FEDERAL REPUBLIC OF NIGERIA OFFICIAL GAZETTE</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -13157,12 +13199,12 @@
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13182,12 +13224,12 @@
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -13207,12 +13249,12 @@
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 8, Text length: 0)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
@@ -13232,12 +13274,12 @@
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 8, Text length: 0)</t>
         </is>
       </c>
     </row>
@@ -13257,18 +13299,18 @@
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B251" s="13" t="inlineStr">
         <is>
@@ -13277,17 +13319,17 @@
       </c>
       <c r="C251" s="13" t="inlineStr">
         <is>
-          <t>Environmental Impact Assessment Act</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -13307,12 +13349,12 @@
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://www.policyvault.africa/policy/environmental-impact-assessment-act-2/ (Redirect chain length: 1)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13379,7 @@
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Redirect detected (healthy_redirect) to: https://www.policyvault.africa/policy/environmental-impact-assessment-act-2/ (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
@@ -13357,12 +13399,12 @@
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.policyvault.africa) (Domain www.policyvault.africa registered under Nigeria)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -13382,12 +13424,12 @@
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Environmental Impact Assessment Act (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (www.policyvault.africa) (Domain www.policyvault.africa registered under Nigeria)</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13449,12 @@
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Regulatory identity: Environmental Impact Assessment Act (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
@@ -13432,18 +13474,18 @@
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E257" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://nesrea.gov.ng/policies-guidelines/ (Candidate title: 'NESREA Official Environmental Regulations and Guidelines (Nigeria)', Verified: True)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B258" s="13" t="inlineStr">
         <is>
@@ -13452,17 +13494,17 @@
       </c>
       <c r="C258" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Replacement candidate identified: https://nesrea.gov.ng/policies-guidelines/ (Candidate title: 'NESREA Official Environmental Regulations and Guidelines (Nigeria)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -13477,17 +13519,17 @@
       </c>
       <c r="C259" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>www.cac.gov.ng</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E259" s="13" t="inlineStr">
         <is>
-          <t>HTTP None (CONNECTION_ERROR) (Content-Type: , Latency: 0ms)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13502,17 +13544,17 @@
       </c>
       <c r="C260" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>www.cac.gov.ng</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -13527,17 +13569,17 @@
       </c>
       <c r="C261" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>www.cac.gov.ng</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
@@ -13552,23 +13594,23 @@
       </c>
       <c r="C262" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>www.cac.gov.ng</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B263" s="13" t="inlineStr">
         <is>
@@ -13577,23 +13619,23 @@
       </c>
       <c r="C263" s="13" t="inlineStr">
         <is>
-          <t>Policies &amp; Guidelines</t>
+          <t>www.cac.gov.ng</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Regulatory identity: www.cac.gov.ng (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B264" s="13" t="inlineStr">
         <is>
@@ -13602,23 +13644,23 @@
       </c>
       <c r="C264" s="13" t="inlineStr">
         <is>
-          <t>Policies &amp; Guidelines</t>
+          <t>www.cac.gov.ng</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Redirect detected (healthy_redirect) to: https://nesrea.gov.ng/policies-guidelines/ (Redirect chain length: 1)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B265" s="13" t="inlineStr">
         <is>
@@ -13627,17 +13669,17 @@
       </c>
       <c r="C265" s="13" t="inlineStr">
         <is>
-          <t>Policies &amp; Guidelines</t>
+          <t>www.cac.gov.ng</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Replacement candidate identified: https://icrp.cac.gov.ng/cama (Candidate title: 'Corporate Affairs Commission (CAC) CAMA 2020 Portal', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -13657,12 +13699,12 @@
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13682,12 +13724,12 @@
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E267" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: Policies &amp; Guidelines (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
+          <t>Redirect detected (healthy_redirect) to: https://nesrea.gov.ng/policies-guidelines/ (Redirect chain length: 1)</t>
         </is>
       </c>
     </row>
@@ -13707,18 +13749,18 @@
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B269" s="13" t="inlineStr">
         <is>
@@ -13727,23 +13769,23 @@
       </c>
       <c r="C269" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Policies &amp; Guidelines</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E269" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (National Environmental Standards and Regulations Enforcement Agency (NESREA)) (Domain nesrea.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B270" s="13" t="inlineStr">
         <is>
@@ -13752,23 +13794,23 @@
       </c>
       <c r="C270" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Policies &amp; Guidelines</t>
         </is>
       </c>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Regulatory identity: Policies &amp; Guidelines (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: National Environmental Standards and Regulations Enforcement Agency (NESREA))</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B271" s="13" t="inlineStr">
         <is>
@@ -13777,17 +13819,17 @@
       </c>
       <c r="C271" s="13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Policies &amp; Guidelines</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E271" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (unfccc.int) (Domain unfccc.int registered under Nigeria)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: National Environmental Standards and Regulations Enforcement Agency (NESREA) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -13807,12 +13849,12 @@
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 5, Text length: 0)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -13832,12 +13874,12 @@
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E273" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -13857,12 +13899,12 @@
       </c>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_3_COMMERCIAL_AGGREGATOR (unfccc.int) (Domain unfccc.int registered under Nigeria)</t>
         </is>
       </c>
     </row>
@@ -13882,18 +13924,18 @@
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>DISCOVERY</t>
+          <t>DOCUMENT</t>
         </is>
       </c>
       <c r="E275" s="13" t="inlineStr">
         <is>
-          <t>Replacement candidate identified: https://unfccc.int/sites/default/files/NDC/2022-06/Nigeria_Updated_NDC_2021.pdf (Candidate title: 'Nigeria Updated NDC 2021', Verified: False)</t>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 5, Text length: 0)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B276" s="13" t="inlineStr">
         <is>
@@ -13902,23 +13944,23 @@
       </c>
       <c r="C276" s="13" t="inlineStr">
         <is>
-          <t>www.cbn.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: UNKNOWN)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B277" s="13" t="inlineStr">
         <is>
@@ -13927,23 +13969,23 @@
       </c>
       <c r="C277" s="13" t="inlineStr">
         <is>
-          <t>www.cbn.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E277" s="13" t="inlineStr">
         <is>
-          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority association is unconfirmed or secondary: UNKNOWN; Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B278" s="13" t="inlineStr">
         <is>
@@ -13952,17 +13994,17 @@
       </c>
       <c r="C278" s="13" t="inlineStr">
         <is>
-          <t>www.cbn.gov.ng</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of Nigeria (CBN)) (Domain www.cbn.gov.ng registered under Nigeria)</t>
+          <t>Replacement candidate identified: https://unfccc.int/sites/default/files/NDC/2022-06/Nigeria_Updated_NDC_2021.pdf (Candidate title: 'Nigeria Updated NDC 2021', Verified: False)</t>
         </is>
       </c>
     </row>
@@ -13982,12 +14024,12 @@
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>BROWSER</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E279" s="13" t="inlineStr">
         <is>
-          <t>Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -14007,12 +14049,12 @@
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: www.cbn.gov.ng (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Central Bank of Nigeria (CBN))</t>
+          <t>HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)</t>
         </is>
       </c>
     </row>
@@ -14032,18 +14074,18 @@
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>CURRENTNESS</t>
+          <t>AUTHORITY</t>
         </is>
       </c>
       <c r="E281" s="13" t="inlineStr">
         <is>
-          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of Nigeria (CBN) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of Nigeria (CBN)) (Domain www.cbn.gov.ng registered under Nigeria)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B282" s="13" t="inlineStr">
         <is>
@@ -14052,23 +14094,23 @@
       </c>
       <c r="C282" s="13" t="inlineStr">
         <is>
-          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+          <t>www.cbn.gov.ng</t>
         </is>
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>EXTRACTION</t>
+          <t>BROWSER</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
+          <t>Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B283" s="13" t="inlineStr">
         <is>
@@ -14077,23 +14119,23 @@
       </c>
       <c r="C283" s="13" t="inlineStr">
         <is>
-          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+          <t>www.cbn.gov.ng</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>IDENTITY</t>
         </is>
       </c>
       <c r="E283" s="13" t="inlineStr">
         <is>
-          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+          <t>Regulatory identity: www.cbn.gov.ng (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Central Bank of Nigeria (CBN))</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B284" s="13" t="inlineStr">
         <is>
@@ -14102,23 +14144,23 @@
       </c>
       <c r="C284" s="13" t="inlineStr">
         <is>
-          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+          <t>www.cbn.gov.ng</t>
         </is>
       </c>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>AUTHORITY</t>
+          <t>CURRENTNESS</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission Nigeria (SEC NG)) (Domain sec.gov.ng registered under Nigeria)</t>
+          <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of Nigeria (CBN) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B285" s="13" t="inlineStr">
         <is>
@@ -14127,17 +14169,17 @@
       </c>
       <c r="C285" s="13" t="inlineStr">
         <is>
-          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+          <t>www.cbn.gov.ng</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>DISCOVERY</t>
         </is>
       </c>
       <c r="E285" s="13" t="inlineStr">
         <is>
-          <t>PDF document verified with magic bytes %PDF- (Pages: 12, Text length: 5000)</t>
+          <t>Replacement candidate identified: https://www.cbn.gov.ng/documents/circulars.html (Candidate title: 'Central Bank of Nigeria (CBN) Circulars (FPR/DIR/CIR/GEN/01/33 - NSBP)', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14199,12 @@
       </c>
       <c r="D286" s="12" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
+          <t>EXTRACTION</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Regulatory identity: NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission Nigeria (SEC NG))</t>
+          <t>Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')</t>
         </is>
       </c>
     </row>
@@ -14182,10 +14224,110 @@
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="E287" s="13" t="inlineStr">
+        <is>
+          <t>HTTP 200 (LIVE) (Content-Type: application/pdf, Latency: 0ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B288" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C288" s="13" t="inlineStr">
+        <is>
+          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+        </is>
+      </c>
+      <c r="D288" s="12" t="inlineStr">
+        <is>
+          <t>AUTHORITY</t>
+        </is>
+      </c>
+      <c r="E288" s="13" t="inlineStr">
+        <is>
+          <t>Source classified as TIER_1_OFFICIAL_REGULATOR (Securities and Exchange Commission Nigeria (SEC NG)) (Domain sec.gov.ng registered under Nigeria)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B289" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C289" s="13" t="inlineStr">
+        <is>
+          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+        </is>
+      </c>
+      <c r="D289" s="12" t="inlineStr">
+        <is>
+          <t>DOCUMENT</t>
+        </is>
+      </c>
+      <c r="E289" s="13" t="inlineStr">
+        <is>
+          <t>PDF document verified with magic bytes %PDF- (Pages: 12, Text length: 5000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B290" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C290" s="13" t="inlineStr">
+        <is>
+          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+        </is>
+      </c>
+      <c r="D290" s="12" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="E290" s="13" t="inlineStr">
+        <is>
+          <t>Regulatory identity: NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION (Rules / Measures) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Securities and Exchange Commission Nigeria (SEC NG))</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B291" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C291" s="13" t="inlineStr">
+        <is>
+          <t>NEW RULE AND SUNDRY AMENDMENTS TO THE RULES AND REGULATIONS OF - THE COMMISSION</t>
+        </is>
+      </c>
+      <c r="D291" s="12" t="inlineStr">
+        <is>
           <t>CURRENTNESS</t>
         </is>
       </c>
-      <c r="E287" s="13" t="inlineStr">
+      <c r="E291" s="13" t="inlineStr">
         <is>
           <t>Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Securities and Exchange Commission Nigeria (SEC NG) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
@@ -14205,7 +14347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14509,39 +14651,119 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>www.cac.gov.ng</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>https://icrp.cac.gov.ng/cama</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Corporate Affairs Commission (CAC) CAMA 2020 Portal</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>REPLACEMENT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>REPLACEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>https://unfccc.int/sites/default/files/NDC/2022-06/Nigeria_Updated_NDC_2021.pdf</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Nigeria Updated NDC 2021</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>CANDIDATE_UNVERIFIED</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>REPLACEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>www.cbn.gov.ng</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cbn.gov.ng/documents/circulars.html</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Central Bank of Nigeria (CBN) Circulars (FPR/DIR/CIR/GEN/01/33 - NSBP)</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>REPLACEMENT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>REPLACEMENT</t>
         </is>
@@ -14742,7 +14964,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="16" t="n">
         <v>1</v>
@@ -15020,7 +15242,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>0</v>
@@ -15053,13 +15275,13 @@
         <v>0</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -15596,7 +15818,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>TIMEOUT</t>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -15618,10 +15840,11 @@
         <is>
           <t>Why was this marked MANUAL_REVIEW?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'China' (Exact match with target jurisdiction: 'China')
-2. (Technical): HTTP None (TIMEOUT) (Content-Type: , Latency: 0ms)
-3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Shanghai Stock Exchange) (Domain www.sse.com.cn registered under China)
-4. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Shanghai Stock Exchange)
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Shanghai Stock Exchange (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+2. (Technical): Redirect detected (healthy_redirect) to: https://static.sse.com.cn/disclosure/listedinfo/announcement/c/20240424_624053.html (Redirect chain length: 1)
+3. (Technical): HTTP 200 (LIVE) (Content-Type: text/html; charset=utf-8, Latency: 0ms)
+4. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Shanghai Stock Exchange) (Domain static.sse.com.cn registered under China)
+5. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Climate &amp; Emissions Disclosure, Population: Listed Companies / Issuers, Authority: Shanghai Stock Exchange)
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Shanghai Stock Exchange (TIER_2_OFFICIAL_EXCHANGE); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
         </is>
       </c>
     </row>
@@ -17623,42 +17846,44 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
+          <t>www.cac.gov.ng</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>BOT_PROTECTION</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>https://www.cac.gov.ng/wp-content/uploads/2020/12/CAMA-NOTE-BOOK-FULL-VERSION.pdf</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>CONNECTION_ERROR</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>Regulatory Lifecycle Status Unknown (Affirmative proof required)</t>
+          <t>Access Blocked / Bot Challenge Unresolved</t>
         </is>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>Why was this marked MANUAL_REVIEW?
+          <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
-2. (Technical): HTTP None (CONNECTION_ERROR) (Content-Type: , Latency: 0ms)
+2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Corporate Affairs Commission (CAC)) (Domain www.cac.gov.ng registered under Nigeria)
-4. (Identity): Regulatory identity: UNKNOWN (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))
-5. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
+5. (Identity): Regulatory identity: www.cac.gov.ng (Guideline / Standard) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Corporate Affairs Commission (CAC))
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Corporate Affairs Commission (CAC) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)
+7. (Discovery): Replacement candidate identified: https://icrp.cac.gov.ng/cama (Candidate title: 'Corporate Affairs Commission (CAC) CAMA 2020 Portal', Verified: True)</t>
         </is>
       </c>
     </row>
@@ -17806,13 +18031,14 @@
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>Why was this marked MANUAL_REVIEW?
+          <t>Why was this marked REPLACE?
 1. (Extraction): Extracted from section 'ESG Legislative Landscape', Country 'Nigeria' (Exact match with target jurisdiction: 'Nigeria')
 2. (Technical): HTTP 403 (BOT_PROTECTION) (Content-Type: text/html; charset=UTF-8, Latency: 0ms)
 3. (Authority): Source classified as TIER_1_OFFICIAL_REGULATOR (Central Bank of Nigeria (CBN)) (Domain www.cbn.gov.ng registered under Nigeria)
 4. (Browser): Rejected technical error page title: 'Just a moment...' (Technical error page title cannot represent the regulatory document.)
 5. (Identity): Regulatory identity: www.cbn.gov.ng (Circular) (Topic: Sustainability &amp; ESG Reporting, Population: Listed Companies / Issuers, Authority: Central Bank of Nigeria (CBN))
-6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of Nigeria (CBN) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)</t>
+6. (Currentness): Lifecycle: UNKNOWN (Lifecycle status unconfirmed due to lack of explicit in-force or supersession evidence.) (Issuing authority verified as authoritative: Central Bank of Nigeria (CBN) (TIER_1_PRIMARY_REGULATOR); Insufficient authoritative lifecycle evidence to confirm active legal status.)
+7. (Discovery): Replacement candidate identified: https://www.cbn.gov.ng/documents/circulars.html (Candidate title: 'Central Bank of Nigeria (CBN) Circulars (FPR/DIR/CIR/GEN/01/33 - NSBP)', Verified: True)</t>
         </is>
       </c>
     </row>
